--- a/research/traditional_assets/database/data/luxembourg/luxembourg_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_packaging_container.xlsx
@@ -1269,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1406,22 +1406,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07251485179629544</v>
+        <v>0.07236777675591548</v>
       </c>
       <c r="C2">
-        <v>5178.887591285558</v>
+        <v>5131.712659787291</v>
       </c>
       <c r="D2">
-        <v>4785.887591285558</v>
+        <v>4796.942659787291</v>
       </c>
       <c r="E2">
-        <v>-4024</v>
+        <v>-3965.77</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>58.23</v>
       </c>
       <c r="G2">
         <v>393</v>
@@ -1442,28 +1442,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.928969</v>
       </c>
       <c r="N2">
-        <v>904.6666666666667</v>
+        <v>901.7376976666667</v>
       </c>
       <c r="O2">
-        <v>225.6238666666667</v>
+        <v>224.8933817980667</v>
       </c>
       <c r="P2">
-        <v>679.0428000000001</v>
+        <v>676.8443158686</v>
       </c>
       <c r="Q2">
-        <v>821.0428000000001</v>
+        <v>818.8443158686</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07251485179629544</v>
+        <v>0.07271739894536917</v>
       </c>
       <c r="T2">
-        <v>0.616971173124606</v>
+        <v>0.6216489363826598</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>308.8686383046959</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1488,22 +1488,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07236777675591548</v>
+        <v>0.07222070171553552</v>
       </c>
       <c r="C3">
-        <v>5131.712659787291</v>
+        <v>5084.588919420436</v>
       </c>
       <c r="D3">
-        <v>4796.942659787291</v>
+        <v>4808.048919420437</v>
       </c>
       <c r="E3">
-        <v>-3965.77</v>
+        <v>-3907.54</v>
       </c>
       <c r="F3">
-        <v>58.23</v>
+        <v>116.46</v>
       </c>
       <c r="G3">
         <v>393</v>
@@ -1524,28 +1524,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M3">
-        <v>2.928969</v>
+        <v>5.857938</v>
       </c>
       <c r="N3">
-        <v>901.7376976666667</v>
+        <v>898.8087286666668</v>
       </c>
       <c r="O3">
-        <v>224.8933817980667</v>
+        <v>224.1628969294667</v>
       </c>
       <c r="P3">
-        <v>676.8443158686</v>
+        <v>674.6458317372001</v>
       </c>
       <c r="Q3">
-        <v>818.8443158686</v>
+        <v>816.6458317372001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07271739894536917</v>
+        <v>0.07292407970973012</v>
       </c>
       <c r="T3">
-        <v>0.6216489363826598</v>
+        <v>0.6264221641970005</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>308.8686383046959</v>
+        <v>154.4343191523479</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,22 +1570,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07222070171553552</v>
+        <v>0.07207362667515554</v>
       </c>
       <c r="C4">
-        <v>5084.588919420436</v>
+        <v>5037.516726575365</v>
       </c>
       <c r="D4">
-        <v>4808.048919420437</v>
+        <v>4819.206726575365</v>
       </c>
       <c r="E4">
-        <v>-3907.54</v>
+        <v>-3849.31</v>
       </c>
       <c r="F4">
-        <v>116.46</v>
+        <v>174.69</v>
       </c>
       <c r="G4">
         <v>393</v>
@@ -1606,28 +1606,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M4">
-        <v>5.857938</v>
+        <v>8.786906999999999</v>
       </c>
       <c r="N4">
-        <v>898.8087286666668</v>
+        <v>895.8797596666667</v>
       </c>
       <c r="O4">
-        <v>224.1628969294667</v>
+        <v>223.4324120608667</v>
       </c>
       <c r="P4">
-        <v>674.6458317372001</v>
+        <v>672.4473476058</v>
       </c>
       <c r="Q4">
-        <v>816.6458317372001</v>
+        <v>814.4473476058</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07292407970973012</v>
+        <v>0.07313502193315005</v>
       </c>
       <c r="T4">
-        <v>0.6264221641970005</v>
+        <v>0.631293809079678</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>154.4343191523479</v>
+        <v>102.956212768232</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,22 +1652,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07207362667515554</v>
+        <v>0.0719265516347756</v>
       </c>
       <c r="C5">
-        <v>5037.516726575365</v>
+        <v>4990.496440958365</v>
       </c>
       <c r="D5">
-        <v>4819.206726575365</v>
+        <v>4830.416440958365</v>
       </c>
       <c r="E5">
-        <v>-3849.31</v>
+        <v>-3791.08</v>
       </c>
       <c r="F5">
-        <v>174.69</v>
+        <v>232.92</v>
       </c>
       <c r="G5">
         <v>393</v>
@@ -1688,28 +1688,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M5">
-        <v>8.786906999999999</v>
+        <v>11.715876</v>
       </c>
       <c r="N5">
-        <v>895.8797596666667</v>
+        <v>892.9507906666668</v>
       </c>
       <c r="O5">
-        <v>223.4324120608667</v>
+        <v>222.7019271922667</v>
       </c>
       <c r="P5">
-        <v>672.4473476058</v>
+        <v>670.2488634744001</v>
       </c>
       <c r="Q5">
-        <v>814.4473476058</v>
+        <v>812.2488634744001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07313502193315005</v>
+        <v>0.07335035878622458</v>
       </c>
       <c r="T5">
-        <v>0.631293809079678</v>
+        <v>0.636266946564078</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>102.956212768232</v>
+        <v>77.21715957617397</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,22 +1734,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0719265516347756</v>
+        <v>0.07177947659439562</v>
       </c>
       <c r="C6">
-        <v>4990.496440958365</v>
+        <v>4943.528425630318</v>
       </c>
       <c r="D6">
-        <v>4830.416440958365</v>
+        <v>4841.678425630318</v>
       </c>
       <c r="E6">
-        <v>-3791.08</v>
+        <v>-3732.85</v>
       </c>
       <c r="F6">
-        <v>232.92</v>
+        <v>291.15</v>
       </c>
       <c r="G6">
         <v>393</v>
@@ -1770,28 +1770,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M6">
-        <v>11.715876</v>
+        <v>14.644845</v>
       </c>
       <c r="N6">
-        <v>892.9507906666668</v>
+        <v>890.0218216666667</v>
       </c>
       <c r="O6">
-        <v>222.7019271922667</v>
+        <v>221.9714423236667</v>
       </c>
       <c r="P6">
-        <v>670.2488634744001</v>
+        <v>668.050379343</v>
       </c>
       <c r="Q6">
-        <v>812.2488634744001</v>
+        <v>810.050379343</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07335035878622458</v>
+        <v>0.07357022904673224</v>
       </c>
       <c r="T6">
-        <v>0.636266946564078</v>
+        <v>0.6413447816797286</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.21715957617397</v>
+        <v>61.77372766093917</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,22 +1816,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07177947659439562</v>
+        <v>0.07163240155401567</v>
       </c>
       <c r="C7">
-        <v>4943.528425630318</v>
+        <v>4896.613047045874</v>
       </c>
       <c r="D7">
-        <v>4841.678425630318</v>
+        <v>4852.993047045874</v>
       </c>
       <c r="E7">
-        <v>-3732.85</v>
+        <v>-3674.62</v>
       </c>
       <c r="F7">
-        <v>291.15</v>
+        <v>349.3800000000001</v>
       </c>
       <c r="G7">
         <v>393</v>
@@ -1852,28 +1852,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M7">
-        <v>14.644845</v>
+        <v>17.573814</v>
       </c>
       <c r="N7">
-        <v>890.0218216666667</v>
+        <v>887.0928526666668</v>
       </c>
       <c r="O7">
-        <v>221.9714423236667</v>
+        <v>221.2409574550667</v>
       </c>
       <c r="P7">
-        <v>668.050379343</v>
+        <v>665.8518952116001</v>
       </c>
       <c r="Q7">
-        <v>810.050379343</v>
+        <v>807.8518952116001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07357022904673224</v>
+        <v>0.07379477739788901</v>
       </c>
       <c r="T7">
-        <v>0.6413447816797286</v>
+        <v>0.6465306558403929</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>61.77372766093917</v>
+        <v>51.47810638411597</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,22 +1898,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07163240155401567</v>
+        <v>0.07148532651363573</v>
       </c>
       <c r="C8">
-        <v>4896.613047045874</v>
+        <v>4849.750675093212</v>
       </c>
       <c r="D8">
-        <v>4852.993047045874</v>
+        <v>4864.360675093211</v>
       </c>
       <c r="E8">
-        <v>-3674.62</v>
+        <v>-3616.39</v>
       </c>
       <c r="F8">
-        <v>349.38</v>
+        <v>407.61</v>
       </c>
       <c r="G8">
         <v>393</v>
@@ -1934,28 +1934,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M8">
-        <v>17.573814</v>
+        <v>20.502783</v>
       </c>
       <c r="N8">
-        <v>887.0928526666668</v>
+        <v>884.1638836666667</v>
       </c>
       <c r="O8">
-        <v>221.2409574550667</v>
+        <v>220.5104725864667</v>
       </c>
       <c r="P8">
-        <v>665.8518952116001</v>
+        <v>663.6534110802</v>
       </c>
       <c r="Q8">
-        <v>807.8518952116001</v>
+        <v>805.6534110802</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07379477739788901</v>
+        <v>0.07402415474584487</v>
       </c>
       <c r="T8">
-        <v>0.6465306558403929</v>
+        <v>0.6518280541765556</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.47810638411598</v>
+        <v>44.12409118638513</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,22 +1980,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07148532651363572</v>
+        <v>0.07133825147325576</v>
       </c>
       <c r="C9">
-        <v>4849.750675093213</v>
+        <v>4802.941683134351</v>
       </c>
       <c r="D9">
-        <v>4864.360675093212</v>
+        <v>4875.781683134352</v>
       </c>
       <c r="E9">
-        <v>-3616.39</v>
+        <v>-3558.16</v>
       </c>
       <c r="F9">
-        <v>407.61</v>
+        <v>465.84</v>
       </c>
       <c r="G9">
         <v>393</v>
@@ -2016,28 +2016,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M9">
-        <v>20.502783</v>
+        <v>23.431752</v>
       </c>
       <c r="N9">
-        <v>884.1638836666667</v>
+        <v>881.2349146666668</v>
       </c>
       <c r="O9">
-        <v>220.5104725864667</v>
+        <v>219.7799877178667</v>
       </c>
       <c r="P9">
-        <v>663.6534110802</v>
+        <v>661.4549269488001</v>
       </c>
       <c r="Q9">
-        <v>805.6534110802</v>
+        <v>803.4549269488001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07402415474584487</v>
+        <v>0.07425851855788669</v>
       </c>
       <c r="T9">
-        <v>0.6518280541765556</v>
+        <v>0.6572406133461129</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.12409118638512</v>
+        <v>38.60857978808698</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,22 +2062,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07133825147325576</v>
+        <v>0.0711911764328758</v>
       </c>
       <c r="C10">
-        <v>4802.941683134351</v>
+        <v>4756.186448046017</v>
       </c>
       <c r="D10">
-        <v>4875.781683134352</v>
+        <v>4887.256448046017</v>
       </c>
       <c r="E10">
-        <v>-3558.16</v>
+        <v>-3499.93</v>
       </c>
       <c r="F10">
-        <v>465.84</v>
+        <v>524.0699999999999</v>
       </c>
       <c r="G10">
         <v>393</v>
@@ -2098,28 +2098,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M10">
-        <v>23.431752</v>
+        <v>26.36072099999999</v>
       </c>
       <c r="N10">
-        <v>881.2349146666668</v>
+        <v>878.3059456666667</v>
       </c>
       <c r="O10">
-        <v>219.7799877178667</v>
+        <v>219.0495028492667</v>
       </c>
       <c r="P10">
-        <v>661.4549269488001</v>
+        <v>659.2564428174001</v>
       </c>
       <c r="Q10">
-        <v>803.4549269488001</v>
+        <v>801.2564428174001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07425851855788669</v>
+        <v>0.07449803322294044</v>
       </c>
       <c r="T10">
-        <v>0.6572406133461129</v>
+        <v>0.6627721298600562</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.60857978808698</v>
+        <v>34.31873758941066</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,22 +2144,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0711911764328758</v>
+        <v>0.07104410139249584</v>
       </c>
       <c r="C11">
-        <v>4756.186448046017</v>
+        <v>4709.4853502611</v>
       </c>
       <c r="D11">
-        <v>4887.256448046017</v>
+        <v>4898.785350261101</v>
       </c>
       <c r="E11">
-        <v>-3499.93</v>
+        <v>-3441.7</v>
       </c>
       <c r="F11">
-        <v>524.0699999999999</v>
+        <v>582.3</v>
       </c>
       <c r="G11">
         <v>393</v>
@@ -2180,28 +2180,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M11">
-        <v>26.36072099999999</v>
+        <v>29.28969</v>
       </c>
       <c r="N11">
-        <v>878.3059456666667</v>
+        <v>875.3769766666668</v>
       </c>
       <c r="O11">
-        <v>219.0495028492667</v>
+        <v>218.3190179806667</v>
       </c>
       <c r="P11">
-        <v>659.2564428174001</v>
+        <v>657.0579586860001</v>
       </c>
       <c r="Q11">
-        <v>801.2564428174001</v>
+        <v>799.0579586860001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07449803322294044</v>
+        <v>0.07474287043610647</v>
       </c>
       <c r="T11">
-        <v>0.6627721298600562</v>
+        <v>0.6684265689631981</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2218,7 +2218,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.31873758941066</v>
+        <v>30.88686383046959</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,22 +2226,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07104410139249584</v>
+        <v>0.07089702635211587</v>
       </c>
       <c r="C12">
-        <v>4709.4853502611</v>
+        <v>4662.838773810709</v>
       </c>
       <c r="D12">
-        <v>4898.785350261101</v>
+        <v>4910.368773810709</v>
       </c>
       <c r="E12">
-        <v>-3441.7</v>
+        <v>-3383.47</v>
       </c>
       <c r="F12">
-        <v>582.3000000000001</v>
+        <v>640.53</v>
       </c>
       <c r="G12">
         <v>393</v>
@@ -2262,28 +2262,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M12">
-        <v>29.28969</v>
+        <v>32.218659</v>
       </c>
       <c r="N12">
-        <v>875.3769766666668</v>
+        <v>872.4480076666667</v>
       </c>
       <c r="O12">
-        <v>218.3190179806667</v>
+        <v>217.5885331120667</v>
       </c>
       <c r="P12">
-        <v>657.0579586860001</v>
+        <v>654.8594745546001</v>
       </c>
       <c r="Q12">
-        <v>799.0579586860001</v>
+        <v>796.8594745546001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07474287043610647</v>
+        <v>0.07499320960911895</v>
       </c>
       <c r="T12">
-        <v>0.6684265689631981</v>
+        <v>0.6742080741136017</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.88686383046959</v>
+        <v>28.07896711860872</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,22 +2308,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07089702635211587</v>
+        <v>0.07074995131173591</v>
       </c>
       <c r="C13">
-        <v>4662.838773810709</v>
+        <v>4616.247106366795</v>
       </c>
       <c r="D13">
-        <v>4910.368773810709</v>
+        <v>4922.007106366796</v>
       </c>
       <c r="E13">
-        <v>-3383.47</v>
+        <v>-3325.24</v>
       </c>
       <c r="F13">
-        <v>640.53</v>
+        <v>698.76</v>
       </c>
       <c r="G13">
         <v>393</v>
@@ -2344,28 +2344,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M13">
-        <v>32.218659</v>
+        <v>35.147628</v>
       </c>
       <c r="N13">
-        <v>872.4480076666667</v>
+        <v>869.5190386666668</v>
       </c>
       <c r="O13">
-        <v>217.5885331120667</v>
+        <v>216.8580482434667</v>
       </c>
       <c r="P13">
-        <v>654.8594745546001</v>
+        <v>652.6609904232001</v>
       </c>
       <c r="Q13">
-        <v>796.8594745546001</v>
+        <v>794.6609904232001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07499320960911895</v>
+        <v>0.07524923830879081</v>
       </c>
       <c r="T13">
-        <v>0.6742080741136017</v>
+        <v>0.6801209771083327</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.07896711860872</v>
+        <v>25.73905319205799</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,22 +2390,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07074995131173591</v>
+        <v>0.07060287627135595</v>
       </c>
       <c r="C14">
-        <v>4616.247106366795</v>
+        <v>4569.71073928542</v>
       </c>
       <c r="D14">
-        <v>4922.007106366796</v>
+        <v>4933.700739285419</v>
       </c>
       <c r="E14">
-        <v>-3325.24</v>
+        <v>-3267.01</v>
       </c>
       <c r="F14">
-        <v>698.76</v>
+        <v>756.99</v>
       </c>
       <c r="G14">
         <v>393</v>
@@ -2426,28 +2426,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M14">
-        <v>35.147628</v>
+        <v>38.076597</v>
       </c>
       <c r="N14">
-        <v>869.5190386666668</v>
+        <v>866.5900696666667</v>
       </c>
       <c r="O14">
-        <v>216.8580482434667</v>
+        <v>216.1275633748667</v>
       </c>
       <c r="P14">
-        <v>652.6609904232001</v>
+        <v>650.4625062918001</v>
       </c>
       <c r="Q14">
-        <v>794.6609904232001</v>
+        <v>792.4625062918001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07524923830879081</v>
+        <v>0.0755111527256965</v>
       </c>
       <c r="T14">
-        <v>0.6801209771083327</v>
+        <v>0.6861698089075403</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.73905319205799</v>
+        <v>23.75912602343814</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,22 +2472,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07060287627135595</v>
+        <v>0.07045580123097599</v>
       </c>
       <c r="C15">
-        <v>4569.71073928542</v>
+        <v>4523.230067650607</v>
       </c>
       <c r="D15">
-        <v>4933.700739285419</v>
+        <v>4945.450067650607</v>
       </c>
       <c r="E15">
-        <v>-3267.01</v>
+        <v>-3208.78</v>
       </c>
       <c r="F15">
-        <v>756.99</v>
+        <v>815.22</v>
       </c>
       <c r="G15">
         <v>393</v>
@@ -2508,28 +2508,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M15">
-        <v>38.076597</v>
+        <v>41.005566</v>
       </c>
       <c r="N15">
-        <v>866.5900696666667</v>
+        <v>863.6611006666667</v>
       </c>
       <c r="O15">
-        <v>216.1275633748667</v>
+        <v>215.3970785062667</v>
       </c>
       <c r="P15">
-        <v>650.4625062918001</v>
+        <v>648.2640221604</v>
       </c>
       <c r="Q15">
-        <v>792.4625062918001</v>
+        <v>790.2640221604</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0755111527256965</v>
+        <v>0.07577915817555347</v>
       </c>
       <c r="T15">
-        <v>0.6861698089075403</v>
+        <v>0.6923593112137062</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.75912602343814</v>
+        <v>22.06204559319256</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,22 +2554,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07045580123097599</v>
+        <v>0.07030872619059601</v>
       </c>
       <c r="C16">
-        <v>4523.230067650607</v>
+        <v>4476.80549031885</v>
       </c>
       <c r="D16">
-        <v>4945.450067650607</v>
+        <v>4957.25549031885</v>
       </c>
       <c r="E16">
-        <v>-3208.78</v>
+        <v>-3150.55</v>
       </c>
       <c r="F16">
-        <v>815.22</v>
+        <v>873.4500000000002</v>
       </c>
       <c r="G16">
         <v>393</v>
@@ -2590,28 +2590,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M16">
-        <v>41.005566</v>
+        <v>43.934535</v>
       </c>
       <c r="N16">
-        <v>863.6611006666667</v>
+        <v>860.7321316666668</v>
       </c>
       <c r="O16">
-        <v>215.3970785062667</v>
+        <v>214.6665936376667</v>
       </c>
       <c r="P16">
-        <v>648.2640221604</v>
+        <v>646.0655380290001</v>
       </c>
       <c r="Q16">
-        <v>790.2640221604</v>
+        <v>788.0655380290001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07577915817555347</v>
+        <v>0.07605346963599532</v>
       </c>
       <c r="T16">
-        <v>0.6923593112137062</v>
+        <v>0.6986944488682524</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.06204559319256</v>
+        <v>20.59124255364639</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,22 +2636,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07030872619059601</v>
+        <v>0.07016165115021605</v>
       </c>
       <c r="C17">
-        <v>4476.80549031885</v>
+        <v>4430.437409964237</v>
       </c>
       <c r="D17">
-        <v>4957.25549031885</v>
+        <v>4969.117409964238</v>
       </c>
       <c r="E17">
-        <v>-3150.55</v>
+        <v>-3092.32</v>
       </c>
       <c r="F17">
-        <v>873.4499999999999</v>
+        <v>931.6800000000001</v>
       </c>
       <c r="G17">
         <v>393</v>
@@ -2672,28 +2672,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M17">
-        <v>43.934535</v>
+        <v>46.863504</v>
       </c>
       <c r="N17">
-        <v>860.7321316666668</v>
+        <v>857.8031626666667</v>
       </c>
       <c r="O17">
-        <v>214.6665936376667</v>
+        <v>213.9361087690667</v>
       </c>
       <c r="P17">
-        <v>646.0655380290001</v>
+        <v>643.8670538976</v>
       </c>
       <c r="Q17">
-        <v>788.0655380290001</v>
+        <v>785.8670538976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07605346963599532</v>
+        <v>0.07633431232168579</v>
       </c>
       <c r="T17">
-        <v>0.6986944488682524</v>
+        <v>0.7051804231336211</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.59124255364639</v>
+        <v>19.30428989404349</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,22 +2718,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07016165115021605</v>
+        <v>0.07001457610983609</v>
       </c>
       <c r="C18">
-        <v>4430.437409964237</v>
+        <v>4384.126233124245</v>
       </c>
       <c r="D18">
-        <v>4969.117409964238</v>
+        <v>4981.036233124245</v>
       </c>
       <c r="E18">
-        <v>-3092.32</v>
+        <v>-3034.09</v>
       </c>
       <c r="F18">
-        <v>931.6800000000001</v>
+        <v>989.9100000000001</v>
       </c>
       <c r="G18">
         <v>393</v>
@@ -2754,28 +2754,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M18">
-        <v>46.863504</v>
+        <v>49.792473</v>
       </c>
       <c r="N18">
-        <v>857.8031626666667</v>
+        <v>854.8741936666668</v>
       </c>
       <c r="O18">
-        <v>213.9361087690667</v>
+        <v>213.2056239004667</v>
       </c>
       <c r="P18">
-        <v>643.8670538976</v>
+        <v>641.6685697662001</v>
       </c>
       <c r="Q18">
-        <v>785.8670538976</v>
+        <v>783.6685697662001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07633431232168579</v>
+        <v>0.07662192230100735</v>
       </c>
       <c r="T18">
-        <v>0.7051804231336211</v>
+        <v>0.7118226859355048</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.30428989404349</v>
+        <v>18.16874342968799</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,22 +2800,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07001457610983609</v>
+        <v>0.06986750106945615</v>
       </c>
       <c r="C19">
-        <v>4384.126233124245</v>
+        <v>4337.872370246171</v>
       </c>
       <c r="D19">
-        <v>4981.036233124245</v>
+        <v>4993.012370246171</v>
       </c>
       <c r="E19">
-        <v>-3034.09</v>
+        <v>-2975.86</v>
       </c>
       <c r="F19">
-        <v>989.9100000000001</v>
+        <v>1048.14</v>
       </c>
       <c r="G19">
         <v>393</v>
@@ -2836,28 +2836,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M19">
-        <v>49.792473</v>
+        <v>52.721442</v>
       </c>
       <c r="N19">
-        <v>854.8741936666668</v>
+        <v>851.9452246666667</v>
       </c>
       <c r="O19">
-        <v>213.2056239004667</v>
+        <v>212.4751390318667</v>
       </c>
       <c r="P19">
-        <v>641.6685697662001</v>
+        <v>639.4700856348001</v>
       </c>
       <c r="Q19">
-        <v>783.6685697662001</v>
+        <v>781.4700856348001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07662192230100735</v>
+        <v>0.07691654715787336</v>
       </c>
       <c r="T19">
-        <v>0.7118226859355048</v>
+        <v>0.7186269551471905</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.16874342968799</v>
+        <v>17.15936879470532</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,22 +2882,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06986750106945615</v>
+        <v>0.06972042602907619</v>
       </c>
       <c r="C20">
-        <v>4337.872370246172</v>
+        <v>4291.676235734267</v>
       </c>
       <c r="D20">
-        <v>4993.012370246171</v>
+        <v>5005.046235734267</v>
       </c>
       <c r="E20">
-        <v>-2975.86</v>
+        <v>-2917.63</v>
       </c>
       <c r="F20">
-        <v>1048.14</v>
+        <v>1106.37</v>
       </c>
       <c r="G20">
         <v>393</v>
@@ -2918,28 +2918,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M20">
-        <v>52.72144199999999</v>
+        <v>55.65041100000001</v>
       </c>
       <c r="N20">
-        <v>851.9452246666667</v>
+        <v>849.0162556666668</v>
       </c>
       <c r="O20">
-        <v>212.4751390318667</v>
+        <v>211.7446541632667</v>
       </c>
       <c r="P20">
-        <v>639.4700856348001</v>
+        <v>637.2716015034</v>
       </c>
       <c r="Q20">
-        <v>781.4700856348001</v>
+        <v>779.2716015034</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07691654715787336</v>
+        <v>0.0772184467025632</v>
       </c>
       <c r="T20">
-        <v>0.7186269551471905</v>
+        <v>0.7255992310060783</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.15936879470533</v>
+        <v>16.25624412129978</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,22 +2964,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06972042602907619</v>
+        <v>0.06957335098869623</v>
       </c>
       <c r="C21">
-        <v>4291.676235734267</v>
+        <v>4245.538247997517</v>
       </c>
       <c r="D21">
-        <v>5005.046235734267</v>
+        <v>5017.138247997517</v>
       </c>
       <c r="E21">
-        <v>-2917.63</v>
+        <v>-2859.4</v>
       </c>
       <c r="F21">
-        <v>1106.37</v>
+        <v>1164.6</v>
       </c>
       <c r="G21">
         <v>393</v>
@@ -3000,28 +3000,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M21">
-        <v>55.65041100000001</v>
+        <v>58.57938</v>
       </c>
       <c r="N21">
-        <v>849.0162556666668</v>
+        <v>846.0872866666667</v>
       </c>
       <c r="O21">
-        <v>211.7446541632667</v>
+        <v>211.0141692946667</v>
       </c>
       <c r="P21">
-        <v>637.2716015034</v>
+        <v>635.0731173720001</v>
       </c>
       <c r="Q21">
-        <v>779.2716015034</v>
+        <v>777.0731173720001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0772184467025632</v>
+        <v>0.07752789373587028</v>
       </c>
       <c r="T21">
-        <v>0.7255992310060783</v>
+        <v>0.7327458137614384</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.25624412129978</v>
+        <v>15.44343191523479</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,22 +3046,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06957335098869623</v>
+        <v>0.06942627594831627</v>
       </c>
       <c r="C22">
-        <v>4245.538247997517</v>
+        <v>4199.458829498149</v>
       </c>
       <c r="D22">
-        <v>5017.138247997517</v>
+        <v>5029.288829498149</v>
       </c>
       <c r="E22">
-        <v>-2859.4</v>
+        <v>-2801.17</v>
       </c>
       <c r="F22">
-        <v>1164.6</v>
+        <v>1222.83</v>
       </c>
       <c r="G22">
         <v>393</v>
@@ -3082,28 +3082,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M22">
-        <v>58.57938</v>
+        <v>61.508349</v>
       </c>
       <c r="N22">
-        <v>846.0872866666667</v>
+        <v>843.1583176666668</v>
       </c>
       <c r="O22">
-        <v>211.0141692946667</v>
+        <v>210.2836844260667</v>
       </c>
       <c r="P22">
-        <v>635.0731173720001</v>
+        <v>632.8746332406001</v>
       </c>
       <c r="Q22">
-        <v>777.0731173720001</v>
+        <v>774.8746332406001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07752789373587028</v>
+        <v>0.07784517487128641</v>
       </c>
       <c r="T22">
-        <v>0.7327458137614384</v>
+        <v>0.7400733226625037</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.44343191523479</v>
+        <v>14.70803039546171</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,22 +3128,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06942627594831627</v>
+        <v>0.06927920090793629</v>
       </c>
       <c r="C23">
-        <v>4199.458829498149</v>
+        <v>4153.438406800826</v>
       </c>
       <c r="D23">
-        <v>5029.288829498149</v>
+        <v>5041.498406800826</v>
       </c>
       <c r="E23">
-        <v>-2801.17</v>
+        <v>-2742.94</v>
       </c>
       <c r="F23">
-        <v>1222.83</v>
+        <v>1281.06</v>
       </c>
       <c r="G23">
         <v>393</v>
@@ -3164,28 +3164,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M23">
-        <v>61.508349</v>
+        <v>64.43731799999999</v>
       </c>
       <c r="N23">
-        <v>843.1583176666668</v>
+        <v>840.2293486666667</v>
       </c>
       <c r="O23">
-        <v>210.2836844260667</v>
+        <v>209.5531995574667</v>
       </c>
       <c r="P23">
-        <v>632.8746332406001</v>
+        <v>630.6761491092001</v>
       </c>
       <c r="Q23">
-        <v>774.8746332406001</v>
+        <v>772.6761491092001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07784517487128641</v>
+        <v>0.07817059142043116</v>
       </c>
       <c r="T23">
-        <v>0.7400733226625037</v>
+        <v>0.7475887164071862</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.70803039546171</v>
+        <v>14.03948355930436</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,22 +3210,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06927920090793629</v>
+        <v>0.06913212586755635</v>
       </c>
       <c r="C24">
-        <v>4153.438406800826</v>
+        <v>4107.477410622564</v>
       </c>
       <c r="D24">
-        <v>5041.498406800826</v>
+        <v>5053.767410622564</v>
       </c>
       <c r="E24">
-        <v>-2742.94</v>
+        <v>-2684.71</v>
       </c>
       <c r="F24">
-        <v>1281.06</v>
+        <v>1339.29</v>
       </c>
       <c r="G24">
         <v>393</v>
@@ -3246,28 +3246,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M24">
-        <v>64.43731799999999</v>
+        <v>67.366287</v>
       </c>
       <c r="N24">
-        <v>840.2293486666667</v>
+        <v>837.3003796666667</v>
       </c>
       <c r="O24">
-        <v>209.5531995574667</v>
+        <v>208.8227146888667</v>
       </c>
       <c r="P24">
-        <v>630.6761491092001</v>
+        <v>628.4776649778</v>
       </c>
       <c r="Q24">
-        <v>772.6761491092001</v>
+        <v>770.4776649778</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07817059142043116</v>
+        <v>0.07850446034747577</v>
       </c>
       <c r="T24">
-        <v>0.7475887164071862</v>
+        <v>0.7552993151841979</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.03948355930436</v>
+        <v>13.42907123063895</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,22 +3292,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06913212586755635</v>
+        <v>0.06925526682717638</v>
       </c>
       <c r="C25">
-        <v>4107.477410622564</v>
+        <v>4038.970928552176</v>
       </c>
       <c r="D25">
-        <v>5053.767410622564</v>
+        <v>5043.490928552176</v>
       </c>
       <c r="E25">
-        <v>-2684.71</v>
+        <v>-2626.48</v>
       </c>
       <c r="F25">
-        <v>1339.29</v>
+        <v>1397.52</v>
       </c>
       <c r="G25">
         <v>393</v>
@@ -3328,45 +3328,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M25">
-        <v>67.366287</v>
+        <v>72.391536</v>
       </c>
       <c r="N25">
-        <v>837.3003796666667</v>
+        <v>832.2751306666668</v>
       </c>
       <c r="O25">
-        <v>208.8227146888667</v>
+        <v>207.5694175882667</v>
       </c>
       <c r="P25">
-        <v>628.4776649778</v>
+        <v>624.7057130784001</v>
       </c>
       <c r="Q25">
-        <v>770.4776649778</v>
+        <v>766.7057130784001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07850446034747577</v>
+        <v>0.07884711529891629</v>
       </c>
       <c r="T25">
-        <v>0.7552993151841979</v>
+        <v>0.7632128244553417</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.42907123063895</v>
+        <v>12.4968569069548</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,22 +3374,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06925526682717638</v>
+        <v>0.06911945078679642</v>
       </c>
       <c r="C26">
-        <v>4038.970928552176</v>
+        <v>3992.077561729511</v>
       </c>
       <c r="D26">
-        <v>5043.490928552176</v>
+        <v>5054.827561729511</v>
       </c>
       <c r="E26">
-        <v>-2626.48</v>
+        <v>-2568.25</v>
       </c>
       <c r="F26">
-        <v>1397.52</v>
+        <v>1455.75</v>
       </c>
       <c r="G26">
         <v>393</v>
@@ -3410,28 +3410,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M26">
-        <v>72.391536</v>
+        <v>75.40785</v>
       </c>
       <c r="N26">
-        <v>832.2751306666668</v>
+        <v>829.2588166666667</v>
       </c>
       <c r="O26">
-        <v>207.5694175882667</v>
+        <v>206.8171488766667</v>
       </c>
       <c r="P26">
-        <v>624.7057130784001</v>
+        <v>622.44166779</v>
       </c>
       <c r="Q26">
-        <v>766.7057130784001</v>
+        <v>764.44166779</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07884711529891629</v>
+        <v>0.07919890771572856</v>
       </c>
       <c r="T26">
-        <v>0.7632128244553417</v>
+        <v>0.7713373606403825</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.4968569069548</v>
+        <v>11.9969826306766</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,22 +3456,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06911945078679642</v>
+        <v>0.06898363474641646</v>
       </c>
       <c r="C27">
-        <v>3992.077561729511</v>
+        <v>3945.235274124317</v>
       </c>
       <c r="D27">
-        <v>5054.827561729511</v>
+        <v>5066.215274124317</v>
       </c>
       <c r="E27">
-        <v>-2568.25</v>
+        <v>-2510.02</v>
       </c>
       <c r="F27">
-        <v>1455.75</v>
+        <v>1513.98</v>
       </c>
       <c r="G27">
         <v>393</v>
@@ -3492,28 +3492,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M27">
-        <v>75.40785</v>
+        <v>78.424164</v>
       </c>
       <c r="N27">
-        <v>829.2588166666667</v>
+        <v>826.2425026666667</v>
       </c>
       <c r="O27">
-        <v>206.8171488766667</v>
+        <v>206.0648801650667</v>
       </c>
       <c r="P27">
-        <v>622.44166779</v>
+        <v>620.1776225016</v>
       </c>
       <c r="Q27">
-        <v>764.44166779</v>
+        <v>762.1776225016</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07919890771572856</v>
+        <v>0.07956020803569791</v>
       </c>
       <c r="T27">
-        <v>0.7713373606403825</v>
+        <v>0.7796814788844785</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.9969826306766</v>
+        <v>11.53556022180443</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,22 +3538,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06898363474641646</v>
+        <v>0.0688478187060365</v>
       </c>
       <c r="C28">
-        <v>3945.235274124317</v>
+        <v>3898.444411735824</v>
       </c>
       <c r="D28">
-        <v>5066.215274124317</v>
+        <v>5077.654411735824</v>
       </c>
       <c r="E28">
-        <v>-2510.02</v>
+        <v>-2451.79</v>
       </c>
       <c r="F28">
-        <v>1513.98</v>
+        <v>1572.21</v>
       </c>
       <c r="G28">
         <v>393</v>
@@ -3574,28 +3574,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M28">
-        <v>78.424164</v>
+        <v>81.440478</v>
       </c>
       <c r="N28">
-        <v>826.2425026666667</v>
+        <v>823.2261886666668</v>
       </c>
       <c r="O28">
-        <v>206.0648801650667</v>
+        <v>205.3126114534667</v>
       </c>
       <c r="P28">
-        <v>620.1776225016</v>
+        <v>617.9135772132</v>
       </c>
       <c r="Q28">
-        <v>762.1776225016</v>
+        <v>759.9135772132</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07956020803569791</v>
+        <v>0.07993140699457055</v>
       </c>
       <c r="T28">
-        <v>0.7796814788844785</v>
+        <v>0.7882542031078648</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.53556022180443</v>
+        <v>11.10831725062649</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,22 +3620,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0688478187060365</v>
+        <v>0.06871200266565654</v>
       </c>
       <c r="C29">
-        <v>3898.444411735824</v>
+        <v>3851.705323695298</v>
       </c>
       <c r="D29">
-        <v>5077.654411735824</v>
+        <v>5089.145323695298</v>
       </c>
       <c r="E29">
-        <v>-2451.79</v>
+        <v>-2393.56</v>
       </c>
       <c r="F29">
-        <v>1572.21</v>
+        <v>1630.44</v>
       </c>
       <c r="G29">
         <v>393</v>
@@ -3656,28 +3656,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M29">
-        <v>81.440478</v>
+        <v>84.45679200000001</v>
       </c>
       <c r="N29">
-        <v>823.2261886666668</v>
+        <v>820.2098746666668</v>
       </c>
       <c r="O29">
-        <v>205.3126114534667</v>
+        <v>204.5603427418667</v>
       </c>
       <c r="P29">
-        <v>617.9135772132</v>
+        <v>615.6495319248</v>
       </c>
       <c r="Q29">
-        <v>759.9135772132</v>
+        <v>757.6495319248</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07993140699457055</v>
+        <v>0.08031291703563409</v>
       </c>
       <c r="T29">
-        <v>0.7882542031078648</v>
+        <v>0.7970650585596786</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.10831725062649</v>
+        <v>10.71159163453268</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,22 +3702,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06871200266565654</v>
+        <v>0.06857618662527658</v>
       </c>
       <c r="C30">
-        <v>3851.705323695298</v>
+        <v>3805.01836230156</v>
       </c>
       <c r="D30">
-        <v>5089.145323695298</v>
+        <v>5100.68836230156</v>
       </c>
       <c r="E30">
-        <v>-2393.56</v>
+        <v>-2335.33</v>
       </c>
       <c r="F30">
-        <v>1630.44</v>
+        <v>1688.67</v>
       </c>
       <c r="G30">
         <v>393</v>
@@ -3738,28 +3738,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M30">
-        <v>84.45679200000001</v>
+        <v>87.47310600000002</v>
       </c>
       <c r="N30">
-        <v>820.2098746666668</v>
+        <v>817.1935606666667</v>
       </c>
       <c r="O30">
-        <v>204.5603427418667</v>
+        <v>203.8080740302667</v>
       </c>
       <c r="P30">
-        <v>615.6495319248</v>
+        <v>613.3854866364001</v>
       </c>
       <c r="Q30">
-        <v>757.6495319248</v>
+        <v>755.3854866364001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08031291703563409</v>
+        <v>0.08070517383841772</v>
       </c>
       <c r="T30">
-        <v>0.7970650585596786</v>
+        <v>0.806124107122811</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.71159163453268</v>
+        <v>10.34222640575569</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,22 +3784,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06857618662527658</v>
+        <v>0.06844037058489662</v>
       </c>
       <c r="C31">
-        <v>3805.01836230156</v>
+        <v>3758.383883056988</v>
       </c>
       <c r="D31">
-        <v>5100.68836230156</v>
+        <v>5112.283883056988</v>
       </c>
       <c r="E31">
-        <v>-2335.33</v>
+        <v>-2277.1</v>
       </c>
       <c r="F31">
-        <v>1688.67</v>
+        <v>1746.9</v>
       </c>
       <c r="G31">
         <v>393</v>
@@ -3820,28 +3820,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M31">
-        <v>87.47310599999999</v>
+        <v>90.48942</v>
       </c>
       <c r="N31">
-        <v>817.1935606666667</v>
+        <v>814.1772466666667</v>
       </c>
       <c r="O31">
-        <v>203.8080740302667</v>
+        <v>203.0558053186667</v>
       </c>
       <c r="P31">
-        <v>613.3854866364001</v>
+        <v>611.1214413480001</v>
       </c>
       <c r="Q31">
-        <v>755.3854866364001</v>
+        <v>753.1214413480001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08070517383841772</v>
+        <v>0.08110863797842374</v>
       </c>
       <c r="T31">
-        <v>0.8061241071228109</v>
+        <v>0.81544198564489</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.34222640575569</v>
+        <v>9.997485525563837</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,22 +3866,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06844037058489662</v>
+        <v>0.06870012074451666</v>
       </c>
       <c r="C32">
-        <v>3758.383883056988</v>
+        <v>3678.023085288021</v>
       </c>
       <c r="D32">
-        <v>5112.283883056988</v>
+        <v>5090.153085288021</v>
       </c>
       <c r="E32">
-        <v>-2277.1</v>
+        <v>-2218.87</v>
       </c>
       <c r="F32">
-        <v>1746.9</v>
+        <v>1805.13</v>
       </c>
       <c r="G32">
         <v>393</v>
@@ -3902,45 +3902,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M32">
-        <v>90.48942</v>
+        <v>96.57445499999999</v>
       </c>
       <c r="N32">
-        <v>814.1772466666667</v>
+        <v>808.0922116666668</v>
       </c>
       <c r="O32">
-        <v>203.0558053186667</v>
+        <v>201.5381975896667</v>
       </c>
       <c r="P32">
-        <v>611.1214413480001</v>
+        <v>606.5540140770001</v>
       </c>
       <c r="Q32">
-        <v>753.1214413480001</v>
+        <v>748.5540140770001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08110863797842374</v>
+        <v>0.08152379673118357</v>
       </c>
       <c r="T32">
-        <v>0.81544198564489</v>
+        <v>0.8250299476023917</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>9.997485525563837</v>
+        <v>9.367556531037808</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,22 +3948,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06870012074451666</v>
+        <v>0.06857706490413669</v>
       </c>
       <c r="C33">
-        <v>3678.023085288021</v>
+        <v>3630.253548955264</v>
       </c>
       <c r="D33">
-        <v>5090.153085288021</v>
+        <v>5100.613548955264</v>
       </c>
       <c r="E33">
-        <v>-2218.87</v>
+        <v>-2160.64</v>
       </c>
       <c r="F33">
-        <v>1805.13</v>
+        <v>1863.36</v>
       </c>
       <c r="G33">
         <v>393</v>
@@ -3984,28 +3984,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M33">
-        <v>96.57445499999999</v>
+        <v>99.68976000000001</v>
       </c>
       <c r="N33">
-        <v>808.0922116666668</v>
+        <v>804.9769066666668</v>
       </c>
       <c r="O33">
-        <v>201.5381975896667</v>
+        <v>200.7612405226667</v>
       </c>
       <c r="P33">
-        <v>606.5540140770001</v>
+        <v>604.2156661440001</v>
       </c>
       <c r="Q33">
-        <v>748.5540140770001</v>
+        <v>746.2156661440001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08152379673118357</v>
+        <v>0.08195116603549514</v>
       </c>
       <c r="T33">
-        <v>0.8250299476023917</v>
+        <v>0.8348999084409963</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.367556531037808</v>
+        <v>9.074820389442875</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,22 +4030,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06857706490413669</v>
+        <v>0.06845400906375673</v>
       </c>
       <c r="C34">
-        <v>3630.253548955264</v>
+        <v>3582.527094481306</v>
       </c>
       <c r="D34">
-        <v>5100.613548955264</v>
+        <v>5111.117094481306</v>
       </c>
       <c r="E34">
-        <v>-2160.64</v>
+        <v>-2102.41</v>
       </c>
       <c r="F34">
-        <v>1863.36</v>
+        <v>1921.59</v>
       </c>
       <c r="G34">
         <v>393</v>
@@ -4066,28 +4066,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M34">
-        <v>99.68976000000001</v>
+        <v>102.805065</v>
       </c>
       <c r="N34">
-        <v>804.9769066666668</v>
+        <v>801.8616016666667</v>
       </c>
       <c r="O34">
-        <v>200.7612405226667</v>
+        <v>199.9842834556667</v>
       </c>
       <c r="P34">
-        <v>604.2156661440001</v>
+        <v>601.8773182110001</v>
       </c>
       <c r="Q34">
-        <v>746.2156661440001</v>
+        <v>743.8773182110001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08195116603549514</v>
+        <v>0.08239129263247275</v>
       </c>
       <c r="T34">
-        <v>0.8348999084409963</v>
+        <v>0.8450644949762757</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.074820389442875</v>
+        <v>8.799825832187031</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,22 +4112,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06845400906375673</v>
+        <v>0.06833095322337676</v>
       </c>
       <c r="C35">
-        <v>3582.527094481306</v>
+        <v>3534.843988567022</v>
       </c>
       <c r="D35">
-        <v>5111.117094481306</v>
+        <v>5121.663988567022</v>
       </c>
       <c r="E35">
-        <v>-2102.41</v>
+        <v>-2044.18</v>
       </c>
       <c r="F35">
-        <v>1921.59</v>
+        <v>1979.82</v>
       </c>
       <c r="G35">
         <v>393</v>
@@ -4148,28 +4148,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M35">
-        <v>102.805065</v>
+        <v>105.92037</v>
       </c>
       <c r="N35">
-        <v>801.8616016666667</v>
+        <v>798.7462966666667</v>
       </c>
       <c r="O35">
-        <v>199.9842834556667</v>
+        <v>199.2073263886667</v>
       </c>
       <c r="P35">
-        <v>601.8773182110001</v>
+        <v>599.5389702780001</v>
       </c>
       <c r="Q35">
-        <v>743.8773182110001</v>
+        <v>741.5389702780001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08239129263247275</v>
+        <v>0.08284475639905571</v>
       </c>
       <c r="T35">
-        <v>0.8450644949762757</v>
+        <v>0.8555370992853514</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.799825832187031</v>
+        <v>8.541007425358</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,22 +4194,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06833095322337676</v>
+        <v>0.0682078973829968</v>
       </c>
       <c r="C36">
-        <v>3534.843988567022</v>
+        <v>3487.204500119211</v>
       </c>
       <c r="D36">
-        <v>5121.663988567022</v>
+        <v>5132.254500119211</v>
       </c>
       <c r="E36">
-        <v>-2044.18</v>
+        <v>-1985.95</v>
       </c>
       <c r="F36">
-        <v>1979.82</v>
+        <v>2038.05</v>
       </c>
       <c r="G36">
         <v>393</v>
@@ -4230,28 +4230,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M36">
-        <v>105.92037</v>
+        <v>109.035675</v>
       </c>
       <c r="N36">
-        <v>798.7462966666667</v>
+        <v>795.6309916666668</v>
       </c>
       <c r="O36">
-        <v>199.2073263886667</v>
+        <v>198.4303693216667</v>
       </c>
       <c r="P36">
-        <v>599.5389702780001</v>
+        <v>597.2006223450001</v>
       </c>
       <c r="Q36">
-        <v>741.5389702780001</v>
+        <v>739.2006223450001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08284475639905571</v>
+        <v>0.08331217289691817</v>
       </c>
       <c r="T36">
-        <v>0.8555370992853514</v>
+        <v>0.866331937573168</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.541007425358</v>
+        <v>8.296978641776342</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,22 +4276,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0682078973829968</v>
+        <v>0.06808484154261685</v>
       </c>
       <c r="C37">
-        <v>3487.204500119211</v>
+        <v>3439.608900273447</v>
       </c>
       <c r="D37">
-        <v>5132.254500119211</v>
+        <v>5142.888900273448</v>
       </c>
       <c r="E37">
-        <v>-1985.95</v>
+        <v>-1927.72</v>
       </c>
       <c r="F37">
-        <v>2038.05</v>
+        <v>2096.28</v>
       </c>
       <c r="G37">
         <v>393</v>
@@ -4312,28 +4312,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M37">
-        <v>109.035675</v>
+        <v>112.15098</v>
       </c>
       <c r="N37">
-        <v>795.6309916666668</v>
+        <v>792.5156866666667</v>
       </c>
       <c r="O37">
-        <v>198.4303693216667</v>
+        <v>197.6534122546667</v>
       </c>
       <c r="P37">
-        <v>597.2006223450001</v>
+        <v>594.862274412</v>
       </c>
       <c r="Q37">
-        <v>739.2006223450001</v>
+        <v>736.862274412</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08331217289691817</v>
+        <v>0.08379419616033884</v>
       </c>
       <c r="T37">
-        <v>0.866331937573168</v>
+        <v>0.8774641145574789</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.296978641776342</v>
+        <v>8.066507012838111</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,22 +4358,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06808484154261686</v>
+        <v>0.06796178570223689</v>
       </c>
       <c r="C38">
-        <v>3439.608900273447</v>
+        <v>3392.057462417225</v>
       </c>
       <c r="D38">
-        <v>5142.888900273447</v>
+        <v>5153.567462417225</v>
       </c>
       <c r="E38">
-        <v>-1927.72</v>
+        <v>-1869.49</v>
       </c>
       <c r="F38">
-        <v>2096.28</v>
+        <v>2154.51</v>
       </c>
       <c r="G38">
         <v>393</v>
@@ -4394,28 +4394,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M38">
-        <v>112.15098</v>
+        <v>115.266285</v>
       </c>
       <c r="N38">
-        <v>792.5156866666667</v>
+        <v>789.4003816666668</v>
       </c>
       <c r="O38">
-        <v>197.6534122546667</v>
+        <v>196.8764551876667</v>
       </c>
       <c r="P38">
-        <v>594.862274412</v>
+        <v>592.5239264790001</v>
       </c>
       <c r="Q38">
-        <v>736.862274412</v>
+        <v>734.5239264790001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08379419616033884</v>
+        <v>0.08429152174958236</v>
       </c>
       <c r="T38">
-        <v>0.8774641145574789</v>
+        <v>0.8889496939857359</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.066507012838112</v>
+        <v>7.848493309788434</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,22 +4440,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06796178570223689</v>
+        <v>0.06783872986185693</v>
       </c>
       <c r="C39">
-        <v>3392.057462417225</v>
+        <v>3344.550462213376</v>
       </c>
       <c r="D39">
-        <v>5153.567462417225</v>
+        <v>5164.290462213376</v>
       </c>
       <c r="E39">
-        <v>-1869.49</v>
+        <v>-1811.26</v>
       </c>
       <c r="F39">
-        <v>2154.51</v>
+        <v>2212.74</v>
       </c>
       <c r="G39">
         <v>393</v>
@@ -4476,28 +4476,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M39">
-        <v>115.266285</v>
+        <v>118.38159</v>
       </c>
       <c r="N39">
-        <v>789.4003816666668</v>
+        <v>786.2850766666668</v>
       </c>
       <c r="O39">
-        <v>196.8764551876667</v>
+        <v>196.0994981206667</v>
       </c>
       <c r="P39">
-        <v>592.5239264790001</v>
+        <v>590.1855785460001</v>
       </c>
       <c r="Q39">
-        <v>734.5239264790001</v>
+        <v>732.1855785460001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08429152174958236</v>
+        <v>0.08480489009976924</v>
       </c>
       <c r="T39">
-        <v>0.8889496939857359</v>
+        <v>0.9008057759761949</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.848493309788434</v>
+        <v>7.641954012162421</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,22 +4522,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06783872986185693</v>
+        <v>0.06794986122147696</v>
       </c>
       <c r="C40">
-        <v>3344.550462213376</v>
+        <v>3276.634604462475</v>
       </c>
       <c r="D40">
-        <v>5164.290462213376</v>
+        <v>5154.604604462475</v>
       </c>
       <c r="E40">
-        <v>-1811.26</v>
+        <v>-1753.03</v>
       </c>
       <c r="F40">
-        <v>2212.74</v>
+        <v>2270.97</v>
       </c>
       <c r="G40">
         <v>393</v>
@@ -4558,45 +4558,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M40">
-        <v>118.38159</v>
+        <v>123.313671</v>
       </c>
       <c r="N40">
-        <v>786.2850766666668</v>
+        <v>781.3529956666667</v>
       </c>
       <c r="O40">
-        <v>196.0994981206667</v>
+        <v>194.8694371192667</v>
       </c>
       <c r="P40">
-        <v>590.1855785460001</v>
+        <v>586.4835585474</v>
       </c>
       <c r="Q40">
-        <v>732.1855785460001</v>
+        <v>728.4835585474</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08480489009976924</v>
+        <v>0.08533509019914257</v>
       </c>
       <c r="T40">
-        <v>0.9008057759761949</v>
+        <v>0.9130505819663411</v>
       </c>
       <c r="U40">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.641954012162421</v>
+        <v>7.336304720558247</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,22 +4604,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06794986122147696</v>
+        <v>0.06783281018109701</v>
       </c>
       <c r="C41">
-        <v>3276.634604462475</v>
+        <v>3228.607424094488</v>
       </c>
       <c r="D41">
-        <v>5154.604604462475</v>
+        <v>5164.807424094488</v>
       </c>
       <c r="E41">
-        <v>-1753.03</v>
+        <v>-1694.8</v>
       </c>
       <c r="F41">
-        <v>2270.97</v>
+        <v>2329.2</v>
       </c>
       <c r="G41">
         <v>393</v>
@@ -4640,28 +4640,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M41">
-        <v>123.313671</v>
+        <v>126.47556</v>
       </c>
       <c r="N41">
-        <v>781.3529956666667</v>
+        <v>778.1911066666668</v>
       </c>
       <c r="O41">
-        <v>194.8694371192667</v>
+        <v>194.0808620026667</v>
       </c>
       <c r="P41">
-        <v>586.4835585474</v>
+        <v>584.1102446640001</v>
       </c>
       <c r="Q41">
-        <v>728.4835585474</v>
+        <v>726.1102446640001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08533509019914257</v>
+        <v>0.08588296363516168</v>
       </c>
       <c r="T41">
-        <v>0.9130505819663411</v>
+        <v>0.9257035481561589</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.336304720558247</v>
+        <v>7.152897102544292</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,22 +4686,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06783281018109701</v>
+        <v>0.06771575914071704</v>
       </c>
       <c r="C42">
-        <v>3228.607424094488</v>
+        <v>3180.620713943565</v>
       </c>
       <c r="D42">
-        <v>5164.807424094488</v>
+        <v>5175.050713943565</v>
       </c>
       <c r="E42">
-        <v>-1694.8</v>
+        <v>-1636.57</v>
       </c>
       <c r="F42">
-        <v>2329.2</v>
+        <v>2387.43</v>
       </c>
       <c r="G42">
         <v>393</v>
@@ -4722,28 +4722,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M42">
-        <v>126.47556</v>
+        <v>129.637449</v>
       </c>
       <c r="N42">
-        <v>778.1911066666668</v>
+        <v>775.0292176666667</v>
       </c>
       <c r="O42">
-        <v>194.0808620026667</v>
+        <v>193.2922868860667</v>
       </c>
       <c r="P42">
-        <v>584.1102446640001</v>
+        <v>581.7369307806</v>
       </c>
       <c r="Q42">
-        <v>726.1102446640001</v>
+        <v>723.7369307806</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08588296363516168</v>
+        <v>0.08644940905206279</v>
       </c>
       <c r="T42">
-        <v>0.9257035481561589</v>
+        <v>0.9387854284541061</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.152897102544292</v>
+        <v>6.978436197604185</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,22 +4768,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06771575914071704</v>
+        <v>0.06759870810033708</v>
       </c>
       <c r="C43">
-        <v>3180.620713943565</v>
+        <v>3132.674715280245</v>
       </c>
       <c r="D43">
-        <v>5175.050713943565</v>
+        <v>5185.334715280245</v>
       </c>
       <c r="E43">
-        <v>-1636.57</v>
+        <v>-1578.34</v>
       </c>
       <c r="F43">
-        <v>2387.43</v>
+        <v>2445.66</v>
       </c>
       <c r="G43">
         <v>393</v>
@@ -4804,28 +4804,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M43">
-        <v>129.637449</v>
+        <v>132.799338</v>
       </c>
       <c r="N43">
-        <v>775.0292176666667</v>
+        <v>771.8673286666667</v>
       </c>
       <c r="O43">
-        <v>193.2922868860667</v>
+        <v>192.5037117694667</v>
       </c>
       <c r="P43">
-        <v>581.7369307806</v>
+        <v>579.3636168972</v>
       </c>
       <c r="Q43">
-        <v>723.7369307806</v>
+        <v>721.3636168972</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08644940905206279</v>
+        <v>0.08703538706954669</v>
       </c>
       <c r="T43">
-        <v>0.9387854284541061</v>
+        <v>0.9523184080726721</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4842,7 +4842,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.978436197604185</v>
+        <v>6.812282954804087</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,22 +4850,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06759870810033708</v>
+        <v>0.06748165705995712</v>
       </c>
       <c r="C44">
-        <v>3132.674715280245</v>
+        <v>3084.769671296731</v>
       </c>
       <c r="D44">
-        <v>5185.334715280245</v>
+        <v>5195.659671296731</v>
       </c>
       <c r="E44">
-        <v>-1578.34</v>
+        <v>-1520.11</v>
       </c>
       <c r="F44">
-        <v>2445.66</v>
+        <v>2503.89</v>
       </c>
       <c r="G44">
         <v>393</v>
@@ -4886,28 +4886,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M44">
-        <v>132.799338</v>
+        <v>135.961227</v>
       </c>
       <c r="N44">
-        <v>771.8673286666667</v>
+        <v>768.7054396666667</v>
       </c>
       <c r="O44">
-        <v>192.5037117694667</v>
+        <v>191.7151366528667</v>
       </c>
       <c r="P44">
-        <v>579.3636168972</v>
+        <v>576.9903030138</v>
       </c>
       <c r="Q44">
-        <v>721.3636168972</v>
+        <v>718.9903030138</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08703538706954669</v>
+        <v>0.08764192571922302</v>
       </c>
       <c r="T44">
-        <v>0.952318408072672</v>
+        <v>0.9663262290813631</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.812282954804087</v>
+        <v>6.653857769808643</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,22 +4932,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06748165705995712</v>
+        <v>0.06736460601957717</v>
       </c>
       <c r="C45">
-        <v>3084.769671296731</v>
+        <v>3036.90582712605</v>
       </c>
       <c r="D45">
-        <v>5195.659671296731</v>
+        <v>5206.02582712605</v>
       </c>
       <c r="E45">
-        <v>-1520.11</v>
+        <v>-1461.88</v>
       </c>
       <c r="F45">
-        <v>2503.89</v>
+        <v>2562.12</v>
       </c>
       <c r="G45">
         <v>393</v>
@@ -4968,28 +4968,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M45">
-        <v>135.961227</v>
+        <v>139.123116</v>
       </c>
       <c r="N45">
-        <v>768.7054396666667</v>
+        <v>765.5435506666668</v>
       </c>
       <c r="O45">
-        <v>191.7151366528667</v>
+        <v>190.9265615362667</v>
       </c>
       <c r="P45">
-        <v>576.9903030138</v>
+        <v>574.6169891304</v>
       </c>
       <c r="Q45">
-        <v>718.9903030138</v>
+        <v>716.6169891304</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08764192571922302</v>
+        <v>0.08827012646353063</v>
       </c>
       <c r="T45">
-        <v>0.9663262290813631</v>
+        <v>0.9808343294117932</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.653857769808643</v>
+        <v>6.502633729585719</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,22 +5014,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06736460601957717</v>
+        <v>0.0672475549791972</v>
       </c>
       <c r="C46">
-        <v>3036.90582712605</v>
+        <v>2989.083429861453</v>
       </c>
       <c r="D46">
-        <v>5206.02582712605</v>
+        <v>5216.433429861453</v>
       </c>
       <c r="E46">
-        <v>-1461.88</v>
+        <v>-1403.65</v>
       </c>
       <c r="F46">
-        <v>2562.12</v>
+        <v>2620.35</v>
       </c>
       <c r="G46">
         <v>393</v>
@@ -5050,28 +5050,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M46">
-        <v>139.123116</v>
+        <v>142.285005</v>
       </c>
       <c r="N46">
-        <v>765.5435506666668</v>
+        <v>762.3816616666668</v>
       </c>
       <c r="O46">
-        <v>190.9265615362667</v>
+        <v>190.1379864196667</v>
       </c>
       <c r="P46">
-        <v>574.6169891304</v>
+        <v>572.2436752470001</v>
       </c>
       <c r="Q46">
-        <v>716.6169891304</v>
+        <v>714.2436752470001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08827012646353063</v>
+        <v>0.08892117087126764</v>
       </c>
       <c r="T46">
-        <v>0.9808343294117932</v>
+        <v>0.9958699970269663</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.502633729585719</v>
+        <v>6.35813075781715</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0672475549791972</v>
+        <v>0.06713050393881724</v>
       </c>
       <c r="C47">
-        <v>2989.083429861453</v>
+        <v>2941.302728576052</v>
       </c>
       <c r="D47">
-        <v>5216.433429861453</v>
+        <v>5226.882728576052</v>
       </c>
       <c r="E47">
-        <v>-1403.65</v>
+        <v>-1345.42</v>
       </c>
       <c r="F47">
-        <v>2620.35</v>
+        <v>2678.58</v>
       </c>
       <c r="G47">
         <v>393</v>
@@ -5132,28 +5132,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M47">
-        <v>142.285005</v>
+        <v>145.446894</v>
       </c>
       <c r="N47">
-        <v>762.3816616666668</v>
+        <v>759.2197726666668</v>
       </c>
       <c r="O47">
-        <v>190.1379864196667</v>
+        <v>189.3494113030667</v>
       </c>
       <c r="P47">
-        <v>572.2436752470001</v>
+        <v>569.8703613636001</v>
       </c>
       <c r="Q47">
-        <v>714.2436752470001</v>
+        <v>711.8703613636001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08892117087126764</v>
+        <v>0.08959632803484674</v>
       </c>
       <c r="T47">
-        <v>0.9958699970269663</v>
+        <v>1.011462541220479</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.35813075781715</v>
+        <v>6.219910523951559</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,22 +5178,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06713050393881724</v>
+        <v>0.06736623489843728</v>
       </c>
       <c r="C48">
-        <v>2941.302728576052</v>
+        <v>2862.071288205681</v>
       </c>
       <c r="D48">
-        <v>5226.882728576052</v>
+        <v>5205.881288205681</v>
       </c>
       <c r="E48">
-        <v>-1345.42</v>
+        <v>-1287.19</v>
       </c>
       <c r="F48">
-        <v>2678.58</v>
+        <v>2736.81</v>
       </c>
       <c r="G48">
         <v>393</v>
@@ -5214,45 +5214,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M48">
-        <v>145.446894</v>
+        <v>151.345593</v>
       </c>
       <c r="N48">
-        <v>759.2197726666668</v>
+        <v>753.3210736666667</v>
       </c>
       <c r="O48">
-        <v>189.3494113030667</v>
+        <v>187.8782757724667</v>
       </c>
       <c r="P48">
-        <v>569.8703613636001</v>
+        <v>565.4427978942001</v>
       </c>
       <c r="Q48">
-        <v>711.8703613636001</v>
+        <v>707.4427978942001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08959632803484674</v>
+        <v>0.09029696282724015</v>
       </c>
       <c r="T48">
-        <v>1.011462541220479</v>
+        <v>1.027643483308087</v>
       </c>
       <c r="U48">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>6.219910523951559</v>
+        <v>5.977489325815167</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,22 +5260,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06736623489843728</v>
+        <v>0.06725668985805733</v>
       </c>
       <c r="C49">
-        <v>2862.071288205681</v>
+        <v>2813.579704559861</v>
       </c>
       <c r="D49">
-        <v>5205.881288205681</v>
+        <v>5215.619704559861</v>
       </c>
       <c r="E49">
-        <v>-1287.19</v>
+        <v>-1228.96</v>
       </c>
       <c r="F49">
-        <v>2736.81</v>
+        <v>2795.04</v>
       </c>
       <c r="G49">
         <v>393</v>
@@ -5296,28 +5296,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M49">
-        <v>151.345593</v>
+        <v>154.565712</v>
       </c>
       <c r="N49">
-        <v>753.3210736666667</v>
+        <v>750.1009546666667</v>
       </c>
       <c r="O49">
-        <v>187.8782757724667</v>
+        <v>187.0751780938667</v>
       </c>
       <c r="P49">
-        <v>565.4427978942001</v>
+        <v>563.0257765727999</v>
       </c>
       <c r="Q49">
-        <v>707.4427978942001</v>
+        <v>705.0257765727999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09029696282724015</v>
+        <v>0.09102454511164869</v>
       </c>
       <c r="T49">
-        <v>1.027643483308087</v>
+        <v>1.044446769322141</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.977489325815167</v>
+        <v>5.852958298194017</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,22 +5342,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06725668985805733</v>
+        <v>0.06714714481767735</v>
       </c>
       <c r="C50">
-        <v>2813.579704559861</v>
+        <v>2765.124623664421</v>
       </c>
       <c r="D50">
-        <v>5215.619704559861</v>
+        <v>5225.394623664421</v>
       </c>
       <c r="E50">
-        <v>-1228.96</v>
+        <v>-1170.73</v>
       </c>
       <c r="F50">
-        <v>2795.04</v>
+        <v>2853.27</v>
       </c>
       <c r="G50">
         <v>393</v>
@@ -5378,28 +5378,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M50">
-        <v>154.565712</v>
+        <v>157.785831</v>
       </c>
       <c r="N50">
-        <v>750.1009546666668</v>
+        <v>746.8808356666667</v>
       </c>
       <c r="O50">
-        <v>187.0751780938667</v>
+        <v>186.2720804152667</v>
       </c>
       <c r="P50">
-        <v>563.0257765728001</v>
+        <v>560.6087552514</v>
       </c>
       <c r="Q50">
-        <v>705.0257765728001</v>
+        <v>702.6087552514</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09102454511164869</v>
+        <v>0.09178066003466148</v>
       </c>
       <c r="T50">
-        <v>1.044446769322141</v>
+        <v>1.061909007728903</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.852958298194019</v>
+        <v>5.733510169659446</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,22 +5424,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06714714481767735</v>
+        <v>0.0670375997772974</v>
       </c>
       <c r="C51">
-        <v>2765.124623664421</v>
+        <v>2716.706251140985</v>
       </c>
       <c r="D51">
-        <v>5225.394623664421</v>
+        <v>5235.206251140985</v>
       </c>
       <c r="E51">
-        <v>-1170.73</v>
+        <v>-1112.5</v>
       </c>
       <c r="F51">
-        <v>2853.27</v>
+        <v>2911.5</v>
       </c>
       <c r="G51">
         <v>393</v>
@@ -5460,28 +5460,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M51">
-        <v>157.785831</v>
+        <v>161.00595</v>
       </c>
       <c r="N51">
-        <v>746.8808356666667</v>
+        <v>743.6607166666668</v>
       </c>
       <c r="O51">
-        <v>186.2720804152667</v>
+        <v>185.4689827366667</v>
       </c>
       <c r="P51">
-        <v>560.6087552514</v>
+        <v>558.1917339300001</v>
       </c>
       <c r="Q51">
-        <v>702.6087552514</v>
+        <v>700.1917339300001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09178066003466148</v>
+        <v>0.0925670195545948</v>
       </c>
       <c r="T51">
-        <v>1.061909007728903</v>
+        <v>1.080069735671935</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.733510169659446</v>
+        <v>5.618839966266258</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,22 +5506,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0670375997772974</v>
+        <v>0.06692805473691744</v>
       </c>
       <c r="C52">
-        <v>2716.706251140985</v>
+        <v>2668.324794158463</v>
       </c>
       <c r="D52">
-        <v>5235.206251140985</v>
+        <v>5245.054794158463</v>
       </c>
       <c r="E52">
-        <v>-1112.5</v>
+        <v>-1054.27</v>
       </c>
       <c r="F52">
-        <v>2911.5</v>
+        <v>2969.73</v>
       </c>
       <c r="G52">
         <v>393</v>
@@ -5542,28 +5542,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M52">
-        <v>161.00595</v>
+        <v>164.226069</v>
       </c>
       <c r="N52">
-        <v>743.6607166666668</v>
+        <v>740.4405976666667</v>
       </c>
       <c r="O52">
-        <v>185.4689827366667</v>
+        <v>184.6658850580667</v>
       </c>
       <c r="P52">
-        <v>558.1917339300001</v>
+        <v>555.7747126086</v>
       </c>
       <c r="Q52">
-        <v>700.1917339300001</v>
+        <v>697.7747126086</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0925670195545948</v>
+        <v>0.09338547538146416</v>
       </c>
       <c r="T52">
-        <v>1.080069735671935</v>
+        <v>1.098971717816724</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.618839966266258</v>
+        <v>5.50866663359437</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,22 +5588,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06692805473691744</v>
+        <v>0.06681850969653746</v>
       </c>
       <c r="C53">
-        <v>2668.324794158463</v>
+        <v>2619.980461447613</v>
       </c>
       <c r="D53">
-        <v>5245.054794158463</v>
+        <v>5254.940461447613</v>
       </c>
       <c r="E53">
-        <v>-1054.27</v>
+        <v>-996.04</v>
       </c>
       <c r="F53">
-        <v>2969.73</v>
+        <v>3027.96</v>
       </c>
       <c r="G53">
         <v>393</v>
@@ -5624,28 +5624,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M53">
-        <v>164.226069</v>
+        <v>167.446188</v>
       </c>
       <c r="N53">
-        <v>740.4405976666667</v>
+        <v>737.2204786666667</v>
       </c>
       <c r="O53">
-        <v>184.6658850580667</v>
+        <v>183.8627873794667</v>
       </c>
       <c r="P53">
-        <v>555.7747126086</v>
+        <v>553.3576912872001</v>
       </c>
       <c r="Q53">
-        <v>697.7747126086</v>
+        <v>695.3576912872001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09338547538146416</v>
+        <v>0.09423803353445308</v>
       </c>
       <c r="T53">
-        <v>1.098971717816724</v>
+        <v>1.118661282550879</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.50866663359437</v>
+        <v>5.402730736794478</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,22 +5670,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06681850969653746</v>
+        <v>0.06670896465615751</v>
       </c>
       <c r="C54">
-        <v>2619.980461447613</v>
+        <v>2571.673463315793</v>
       </c>
       <c r="D54">
-        <v>5254.940461447613</v>
+        <v>5264.863463315793</v>
       </c>
       <c r="E54">
-        <v>-996.04</v>
+        <v>-937.8099999999999</v>
       </c>
       <c r="F54">
-        <v>3027.96</v>
+        <v>3086.19</v>
       </c>
       <c r="G54">
         <v>393</v>
@@ -5706,28 +5706,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M54">
-        <v>167.446188</v>
+        <v>170.666307</v>
       </c>
       <c r="N54">
-        <v>737.2204786666667</v>
+        <v>734.0003596666668</v>
       </c>
       <c r="O54">
-        <v>183.8627873794667</v>
+        <v>183.0596897008667</v>
       </c>
       <c r="P54">
-        <v>553.3576912872001</v>
+        <v>550.9406699658001</v>
       </c>
       <c r="Q54">
-        <v>695.3576912872001</v>
+        <v>692.9406699658001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09423803353445308</v>
+        <v>0.09512687075778195</v>
       </c>
       <c r="T54">
-        <v>1.118661282550879</v>
+        <v>1.139188701103509</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5744,7 +5744,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.402730736794478</v>
+        <v>5.300792421005903</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,22 +5752,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06670896465615751</v>
+        <v>0.06659941961577756</v>
       </c>
       <c r="C55">
-        <v>2571.673463315793</v>
+        <v>2523.404011661874</v>
       </c>
       <c r="D55">
-        <v>5264.863463315793</v>
+        <v>5274.824011661874</v>
       </c>
       <c r="E55">
-        <v>-937.8099999999999</v>
+        <v>-879.5799999999999</v>
       </c>
       <c r="F55">
-        <v>3086.19</v>
+        <v>3144.42</v>
       </c>
       <c r="G55">
         <v>393</v>
@@ -5788,28 +5788,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M55">
-        <v>170.666307</v>
+        <v>173.886426</v>
       </c>
       <c r="N55">
-        <v>734.0003596666668</v>
+        <v>730.7802406666667</v>
       </c>
       <c r="O55">
-        <v>183.0596897008667</v>
+        <v>182.2565920222667</v>
       </c>
       <c r="P55">
-        <v>550.9406699658001</v>
+        <v>548.5236486444001</v>
       </c>
       <c r="Q55">
-        <v>692.9406699658001</v>
+        <v>690.5236486444001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09512687075778195</v>
+        <v>0.09605435307777729</v>
       </c>
       <c r="T55">
-        <v>1.139188701103509</v>
+        <v>1.160608616114949</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.300792421005903</v>
+        <v>5.202629598394683</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,22 +5834,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06659941961577756</v>
+        <v>0.0664898745753976</v>
       </c>
       <c r="C56">
-        <v>2523.404011661874</v>
+        <v>2475.172319991334</v>
       </c>
       <c r="D56">
-        <v>5274.824011661874</v>
+        <v>5284.822319991334</v>
       </c>
       <c r="E56">
-        <v>-879.5799999999999</v>
+        <v>-821.3499999999999</v>
       </c>
       <c r="F56">
-        <v>3144.42</v>
+        <v>3202.65</v>
       </c>
       <c r="G56">
         <v>393</v>
@@ -5870,28 +5870,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M56">
-        <v>173.886426</v>
+        <v>177.106545</v>
       </c>
       <c r="N56">
-        <v>730.7802406666667</v>
+        <v>727.5601216666668</v>
       </c>
       <c r="O56">
-        <v>182.2565920222667</v>
+        <v>181.4534943436667</v>
       </c>
       <c r="P56">
-        <v>548.5236486444001</v>
+        <v>546.1066273230001</v>
       </c>
       <c r="Q56">
-        <v>690.5236486444001</v>
+        <v>688.1066273230001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09605435307777729</v>
+        <v>0.09702305683421689</v>
       </c>
       <c r="T56">
-        <v>1.160608616114949</v>
+        <v>1.18298052734912</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.202629598394683</v>
+        <v>5.108036332969325</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,22 +5916,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0664898745753976</v>
+        <v>0.06638032953501763</v>
       </c>
       <c r="C57">
-        <v>2475.172319991334</v>
+        <v>2426.978603431493</v>
       </c>
       <c r="D57">
-        <v>5284.822319991334</v>
+        <v>5294.858603431493</v>
       </c>
       <c r="E57">
-        <v>-821.3499999999999</v>
+        <v>-763.1199999999999</v>
       </c>
       <c r="F57">
-        <v>3202.65</v>
+        <v>3260.88</v>
       </c>
       <c r="G57">
         <v>393</v>
@@ -5952,28 +5952,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M57">
-        <v>177.106545</v>
+        <v>180.326664</v>
       </c>
       <c r="N57">
-        <v>727.5601216666668</v>
+        <v>724.3400026666667</v>
       </c>
       <c r="O57">
-        <v>181.4534943436667</v>
+        <v>180.6503966650667</v>
       </c>
       <c r="P57">
-        <v>546.1066273230001</v>
+        <v>543.6896060015999</v>
       </c>
       <c r="Q57">
-        <v>688.1066273230001</v>
+        <v>685.6896060015999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09702305683421689</v>
+        <v>0.09803579257958554</v>
       </c>
       <c r="T57">
-        <v>1.18298052734912</v>
+        <v>1.206369343639389</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.108036332969325</v>
+        <v>5.016821398452015</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,22 +5998,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06638032953501763</v>
+        <v>0.06627078449463768</v>
       </c>
       <c r="C58">
-        <v>2426.978603431493</v>
+        <v>2378.823078746959</v>
       </c>
       <c r="D58">
-        <v>5294.858603431493</v>
+        <v>5304.93307874696</v>
       </c>
       <c r="E58">
-        <v>-763.1199999999999</v>
+        <v>-704.8899999999994</v>
       </c>
       <c r="F58">
-        <v>3260.88</v>
+        <v>3319.110000000001</v>
       </c>
       <c r="G58">
         <v>393</v>
@@ -6034,28 +6034,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M58">
-        <v>180.326664</v>
+        <v>183.546783</v>
       </c>
       <c r="N58">
-        <v>724.3400026666667</v>
+        <v>721.1198836666667</v>
       </c>
       <c r="O58">
-        <v>180.6503966650667</v>
+        <v>179.8472989864667</v>
       </c>
       <c r="P58">
-        <v>543.6896060015999</v>
+        <v>541.2725846802</v>
       </c>
       <c r="Q58">
-        <v>685.6896060015999</v>
+        <v>683.2725846802</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09803579257958554</v>
+        <v>0.09909563231311087</v>
       </c>
       <c r="T58">
-        <v>1.206369343639389</v>
+        <v>1.230846011850136</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.016821398452015</v>
+        <v>4.928806987952857</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,22 +6080,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06627078449463768</v>
+        <v>0.0661612394542577</v>
       </c>
       <c r="C59">
-        <v>2378.823078746959</v>
+        <v>2330.705964355231</v>
       </c>
       <c r="D59">
-        <v>5304.93307874696</v>
+        <v>5315.045964355231</v>
       </c>
       <c r="E59">
-        <v>-704.8899999999994</v>
+        <v>-646.6599999999994</v>
       </c>
       <c r="F59">
-        <v>3319.110000000001</v>
+        <v>3377.340000000001</v>
       </c>
       <c r="G59">
         <v>393</v>
@@ -6116,28 +6116,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M59">
-        <v>183.546783</v>
+        <v>186.766902</v>
       </c>
       <c r="N59">
-        <v>721.1198836666667</v>
+        <v>717.8997646666667</v>
       </c>
       <c r="O59">
-        <v>179.8472989864667</v>
+        <v>179.0442013078667</v>
       </c>
       <c r="P59">
-        <v>541.2725846802</v>
+        <v>538.8555633588001</v>
       </c>
       <c r="Q59">
-        <v>683.2725846802</v>
+        <v>680.8555633588001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09909563231311087</v>
+        <v>0.1002059406053755</v>
       </c>
       <c r="T59">
-        <v>1.230846011850136</v>
+        <v>1.256488235689966</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.928806987952857</v>
+        <v>4.843827557126083</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,22 +6162,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06616123945425771</v>
+        <v>0.06605169441387775</v>
       </c>
       <c r="C60">
-        <v>2330.70596435523</v>
+        <v>2282.627480342473</v>
       </c>
       <c r="D60">
-        <v>5315.045964355229</v>
+        <v>5325.197480342473</v>
       </c>
       <c r="E60">
-        <v>-646.6600000000003</v>
+        <v>-588.4300000000003</v>
       </c>
       <c r="F60">
-        <v>3377.34</v>
+        <v>3435.57</v>
       </c>
       <c r="G60">
         <v>393</v>
@@ -6198,28 +6198,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M60">
-        <v>186.766902</v>
+        <v>189.987021</v>
       </c>
       <c r="N60">
-        <v>717.8997646666668</v>
+        <v>714.6796456666667</v>
       </c>
       <c r="O60">
-        <v>179.0442013078667</v>
+        <v>178.2411036292667</v>
       </c>
       <c r="P60">
-        <v>538.8555633588001</v>
+        <v>536.4385420374</v>
       </c>
       <c r="Q60">
-        <v>680.8555633588001</v>
+        <v>678.4385420374</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1002059406053755</v>
+        <v>0.1013704102777506</v>
       </c>
       <c r="T60">
-        <v>1.256488235689965</v>
+        <v>1.283381299717104</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.843827557126085</v>
+        <v>4.761728784971405</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,22 +6244,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06605169441387775</v>
+        <v>0.06594214937349779</v>
       </c>
       <c r="C61">
-        <v>2282.627480342473</v>
+        <v>2234.587848479496</v>
       </c>
       <c r="D61">
-        <v>5325.197480342473</v>
+        <v>5335.387848479496</v>
       </c>
       <c r="E61">
-        <v>-588.4300000000003</v>
+        <v>-530.2000000000003</v>
       </c>
       <c r="F61">
-        <v>3435.57</v>
+        <v>3493.8</v>
       </c>
       <c r="G61">
         <v>393</v>
@@ -6280,28 +6280,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M61">
-        <v>189.987021</v>
+        <v>193.20714</v>
       </c>
       <c r="N61">
-        <v>714.6796456666667</v>
+        <v>711.4595266666668</v>
       </c>
       <c r="O61">
-        <v>178.2411036292667</v>
+        <v>177.4380059506667</v>
       </c>
       <c r="P61">
-        <v>536.4385420374</v>
+        <v>534.0215207160001</v>
       </c>
       <c r="Q61">
-        <v>678.4385420374</v>
+        <v>676.0215207160001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1013704102777506</v>
+        <v>0.1025931034337445</v>
       </c>
       <c r="T61">
-        <v>1.283381299717104</v>
+        <v>1.3116190169456</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.761728784971405</v>
+        <v>4.682366638555215</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,22 +6326,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06594214937349779</v>
+        <v>0.06583260433311783</v>
       </c>
       <c r="C62">
-        <v>2234.587848479496</v>
+        <v>2186.587292237898</v>
       </c>
       <c r="D62">
-        <v>5335.387848479496</v>
+        <v>5345.617292237897</v>
       </c>
       <c r="E62">
-        <v>-530.2000000000003</v>
+        <v>-471.9700000000003</v>
       </c>
       <c r="F62">
-        <v>3493.8</v>
+        <v>3552.03</v>
       </c>
       <c r="G62">
         <v>393</v>
@@ -6362,28 +6362,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M62">
-        <v>193.20714</v>
+        <v>196.427259</v>
       </c>
       <c r="N62">
-        <v>711.4595266666668</v>
+        <v>708.2394076666667</v>
       </c>
       <c r="O62">
-        <v>177.4380059506667</v>
+        <v>176.6349082720667</v>
       </c>
       <c r="P62">
-        <v>534.0215207160001</v>
+        <v>531.6044993946</v>
       </c>
       <c r="Q62">
-        <v>676.0215207160001</v>
+        <v>673.6044993946</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1025931034337445</v>
+        <v>0.1038784988028662</v>
       </c>
       <c r="T62">
-        <v>1.3116190169456</v>
+        <v>1.341304822237096</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.682366638555215</v>
+        <v>4.60560652972644</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,22 +6408,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06583260433311783</v>
+        <v>0.06572305929273786</v>
       </c>
       <c r="C63">
-        <v>2186.587292237898</v>
+        <v>2138.626036806398</v>
       </c>
       <c r="D63">
-        <v>5345.617292237897</v>
+        <v>5355.886036806398</v>
       </c>
       <c r="E63">
-        <v>-471.9700000000003</v>
+        <v>-413.7400000000002</v>
       </c>
       <c r="F63">
-        <v>3552.03</v>
+        <v>3610.26</v>
       </c>
       <c r="G63">
         <v>393</v>
@@ -6444,28 +6444,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M63">
-        <v>196.427259</v>
+        <v>199.647378</v>
       </c>
       <c r="N63">
-        <v>708.2394076666667</v>
+        <v>705.0192886666667</v>
       </c>
       <c r="O63">
-        <v>176.6349082720667</v>
+        <v>175.8318105934667</v>
       </c>
       <c r="P63">
-        <v>531.6044993946</v>
+        <v>529.1874780732001</v>
       </c>
       <c r="Q63">
-        <v>673.6044993946</v>
+        <v>671.1874780732001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1038784988028662</v>
+        <v>0.1052315465598365</v>
       </c>
       <c r="T63">
-        <v>1.341304822237096</v>
+        <v>1.372553038333407</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.60560652972644</v>
+        <v>4.53132255344053</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,22 +6490,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06572305929273786</v>
+        <v>0.06679570925235791</v>
       </c>
       <c r="C64">
-        <v>2138.626036806398</v>
+        <v>1981.512727774059</v>
       </c>
       <c r="D64">
-        <v>5355.886036806398</v>
+        <v>5257.002727774059</v>
       </c>
       <c r="E64">
-        <v>-413.7400000000002</v>
+        <v>-355.5099999999998</v>
       </c>
       <c r="F64">
-        <v>3610.26</v>
+        <v>3668.49</v>
       </c>
       <c r="G64">
         <v>393</v>
@@ -6526,45 +6526,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M64">
-        <v>199.647378</v>
+        <v>212.038722</v>
       </c>
       <c r="N64">
-        <v>705.0192886666667</v>
+        <v>692.6279446666667</v>
       </c>
       <c r="O64">
-        <v>175.8318105934667</v>
+        <v>172.7414093998667</v>
       </c>
       <c r="P64">
-        <v>529.1874780732001</v>
+        <v>519.8865352668</v>
       </c>
       <c r="Q64">
-        <v>671.1874780732001</v>
+        <v>661.8865352668</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1052315465598365</v>
+        <v>0.1066577320333998</v>
       </c>
       <c r="T64">
-        <v>1.372553038333407</v>
+        <v>1.40549034719168</v>
       </c>
       <c r="U64">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.53132255344053</v>
+        <v>4.266516314254463</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,22 +6572,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06679570925235791</v>
+        <v>0.06670492921197796</v>
       </c>
       <c r="C65">
-        <v>1981.512727774059</v>
+        <v>1931.509724775759</v>
       </c>
       <c r="D65">
-        <v>5257.002727774059</v>
+        <v>5265.22972477576</v>
       </c>
       <c r="E65">
-        <v>-355.5099999999998</v>
+        <v>-297.2799999999997</v>
       </c>
       <c r="F65">
-        <v>3668.49</v>
+        <v>3726.72</v>
       </c>
       <c r="G65">
         <v>393</v>
@@ -6608,28 +6608,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M65">
-        <v>212.038722</v>
+        <v>215.404416</v>
       </c>
       <c r="N65">
-        <v>692.6279446666667</v>
+        <v>689.2622506666667</v>
       </c>
       <c r="O65">
-        <v>172.7414093998667</v>
+        <v>171.9020053162667</v>
       </c>
       <c r="P65">
-        <v>519.8865352668</v>
+        <v>517.3602453504</v>
       </c>
       <c r="Q65">
-        <v>661.8865352668</v>
+        <v>659.3602453504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1066577320333998</v>
+        <v>0.1081631500332721</v>
       </c>
       <c r="T65">
-        <v>1.40549034719168</v>
+        <v>1.44025750654208</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.266516314254463</v>
+        <v>4.199851996844236</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,22 +6654,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06670492921197796</v>
+        <v>0.066614149171598</v>
       </c>
       <c r="C66">
-        <v>1931.509724775759</v>
+        <v>1881.532511974313</v>
       </c>
       <c r="D66">
-        <v>5265.22972477576</v>
+        <v>5273.482511974314</v>
       </c>
       <c r="E66">
-        <v>-297.2799999999997</v>
+        <v>-239.0499999999997</v>
       </c>
       <c r="F66">
-        <v>3726.72</v>
+        <v>3784.95</v>
       </c>
       <c r="G66">
         <v>393</v>
@@ -6690,28 +6690,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M66">
-        <v>215.404416</v>
+        <v>218.77011</v>
       </c>
       <c r="N66">
-        <v>689.2622506666667</v>
+        <v>685.8965566666667</v>
       </c>
       <c r="O66">
-        <v>171.9020053162667</v>
+        <v>171.0626012326667</v>
       </c>
       <c r="P66">
-        <v>517.3602453504</v>
+        <v>514.833955434</v>
       </c>
       <c r="Q66">
-        <v>659.3602453504</v>
+        <v>656.833955434</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1081631500332721</v>
+        <v>0.1097545919188514</v>
       </c>
       <c r="T66">
-        <v>1.44025750654208</v>
+        <v>1.477011360712503</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.199851996844236</v>
+        <v>4.135238889200479</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,22 +6736,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.066614149171598</v>
+        <v>0.06652336913121802</v>
       </c>
       <c r="C67">
-        <v>1881.532511974313</v>
+        <v>1831.581210831738</v>
       </c>
       <c r="D67">
-        <v>5273.482511974314</v>
+        <v>5281.761210831738</v>
       </c>
       <c r="E67">
-        <v>-239.0499999999997</v>
+        <v>-180.8199999999997</v>
       </c>
       <c r="F67">
-        <v>3784.95</v>
+        <v>3843.18</v>
       </c>
       <c r="G67">
         <v>393</v>
@@ -6772,28 +6772,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M67">
-        <v>218.77011</v>
+        <v>222.135804</v>
       </c>
       <c r="N67">
-        <v>685.8965566666667</v>
+        <v>682.5308626666667</v>
       </c>
       <c r="O67">
-        <v>171.0626012326667</v>
+        <v>170.2231971490667</v>
       </c>
       <c r="P67">
-        <v>514.833955434</v>
+        <v>512.3076655176001</v>
       </c>
       <c r="Q67">
-        <v>656.833955434</v>
+        <v>654.3076655176001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1097545919188514</v>
+        <v>0.1114396480329942</v>
       </c>
       <c r="T67">
-        <v>1.477011360712503</v>
+        <v>1.515927206304716</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.135238889200479</v>
+        <v>4.072583754515623</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,22 +6818,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06652336913121802</v>
+        <v>0.06643258909083807</v>
       </c>
       <c r="C68">
-        <v>1831.581210831738</v>
+        <v>1781.655943573963</v>
       </c>
       <c r="D68">
-        <v>5281.761210831738</v>
+        <v>5290.065943573964</v>
       </c>
       <c r="E68">
-        <v>-180.8199999999997</v>
+        <v>-122.5899999999997</v>
       </c>
       <c r="F68">
-        <v>3843.18</v>
+        <v>3901.41</v>
       </c>
       <c r="G68">
         <v>393</v>
@@ -6854,28 +6854,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M68">
-        <v>222.135804</v>
+        <v>225.501498</v>
       </c>
       <c r="N68">
-        <v>682.5308626666667</v>
+        <v>679.1651686666667</v>
       </c>
       <c r="O68">
-        <v>170.2231971490667</v>
+        <v>169.3837930654667</v>
       </c>
       <c r="P68">
-        <v>512.3076655176001</v>
+        <v>509.7813756012</v>
       </c>
       <c r="Q68">
-        <v>654.3076655176001</v>
+        <v>651.7813756012</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1114396480329942</v>
+        <v>0.1132268287601154</v>
       </c>
       <c r="T68">
-        <v>1.515927206304716</v>
+        <v>1.557201587993426</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.072583754515623</v>
+        <v>4.011798922358674</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,22 +6900,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06643258909083807</v>
+        <v>0.06812823705045809</v>
       </c>
       <c r="C69">
-        <v>1781.655943573963</v>
+        <v>1572.493663961949</v>
       </c>
       <c r="D69">
-        <v>5290.065943573964</v>
+        <v>5139.133663961949</v>
       </c>
       <c r="E69">
-        <v>-122.5899999999997</v>
+        <v>-64.35999999999967</v>
       </c>
       <c r="F69">
-        <v>3901.41</v>
+        <v>3959.64</v>
       </c>
       <c r="G69">
         <v>393</v>
@@ -6936,45 +6936,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M69">
-        <v>225.501498</v>
+        <v>242.725932</v>
       </c>
       <c r="N69">
-        <v>679.1651686666667</v>
+        <v>661.9407346666667</v>
       </c>
       <c r="O69">
-        <v>169.3837930654667</v>
+        <v>165.0880192258667</v>
       </c>
       <c r="P69">
-        <v>509.7813756012</v>
+        <v>496.8527154408</v>
       </c>
       <c r="Q69">
-        <v>651.7813756012</v>
+        <v>638.8527154408</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1132268287601154</v>
+        <v>0.1151257082826816</v>
       </c>
       <c r="T69">
-        <v>1.557201587993426</v>
+        <v>1.601055618537681</v>
       </c>
       <c r="U69">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V69">
         <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>4.011798922358674</v>
+        <v>3.727111723137463</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,22 +6982,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06812823705045809</v>
+        <v>0.06806372801007812</v>
       </c>
       <c r="C70">
-        <v>1572.493663961949</v>
+        <v>1519.847948072757</v>
       </c>
       <c r="D70">
-        <v>5139.133663961949</v>
+        <v>5144.717948072757</v>
       </c>
       <c r="E70">
-        <v>-64.35999999999967</v>
+        <v>-6.129999999999654</v>
       </c>
       <c r="F70">
-        <v>3959.64</v>
+        <v>4017.87</v>
       </c>
       <c r="G70">
         <v>393</v>
@@ -7018,28 +7018,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M70">
-        <v>242.725932</v>
+        <v>246.295431</v>
       </c>
       <c r="N70">
-        <v>661.9407346666667</v>
+        <v>658.3712356666667</v>
       </c>
       <c r="O70">
-        <v>165.0880192258667</v>
+        <v>164.1977861752667</v>
       </c>
       <c r="P70">
-        <v>496.8527154408</v>
+        <v>494.1734494914</v>
       </c>
       <c r="Q70">
-        <v>638.8527154408</v>
+        <v>636.1734494914001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1151257082826816</v>
+        <v>0.1171470961615424</v>
       </c>
       <c r="T70">
-        <v>1.601055618537681</v>
+        <v>1.647738941375113</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.727111723137463</v>
+        <v>3.673095611207934</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,22 +7064,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06806372801007812</v>
+        <v>0.06799921896969818</v>
       </c>
       <c r="C71">
-        <v>1519.847948072757</v>
+        <v>1467.214381371861</v>
       </c>
       <c r="D71">
-        <v>5144.717948072757</v>
+        <v>5150.314381371862</v>
       </c>
       <c r="E71">
-        <v>-6.129999999999654</v>
+        <v>52.10000000000036</v>
       </c>
       <c r="F71">
-        <v>4017.87</v>
+        <v>4076.1</v>
       </c>
       <c r="G71">
         <v>393</v>
@@ -7100,28 +7100,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M71">
-        <v>246.295431</v>
+        <v>249.86493</v>
       </c>
       <c r="N71">
-        <v>658.3712356666667</v>
+        <v>654.8017366666668</v>
       </c>
       <c r="O71">
-        <v>164.1977861752667</v>
+        <v>163.3075531246667</v>
       </c>
       <c r="P71">
-        <v>494.1734494914</v>
+        <v>491.4941835420001</v>
       </c>
       <c r="Q71">
-        <v>636.1734494914001</v>
+        <v>633.4941835420001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1171470961615424</v>
+        <v>0.1193032432323273</v>
       </c>
       <c r="T71">
-        <v>1.647738941375113</v>
+        <v>1.697534485735041</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.673095611207934</v>
+        <v>3.620622816762107</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,22 +7146,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06799921896969818</v>
+        <v>0.06793470992931822</v>
       </c>
       <c r="C72">
-        <v>1467.214381371861</v>
+        <v>1414.593003550169</v>
       </c>
       <c r="D72">
-        <v>5150.314381371862</v>
+        <v>5155.92300355017</v>
       </c>
       <c r="E72">
-        <v>52.10000000000036</v>
+        <v>110.3300000000008</v>
       </c>
       <c r="F72">
-        <v>4076.1</v>
+        <v>4134.330000000001</v>
       </c>
       <c r="G72">
         <v>393</v>
@@ -7182,28 +7182,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M72">
-        <v>249.86493</v>
+        <v>253.4344290000001</v>
       </c>
       <c r="N72">
-        <v>654.8017366666668</v>
+        <v>651.2322376666667</v>
       </c>
       <c r="O72">
-        <v>163.3075531246667</v>
+        <v>162.4173200740667</v>
       </c>
       <c r="P72">
-        <v>491.4941835420001</v>
+        <v>488.8149175926001</v>
       </c>
       <c r="Q72">
-        <v>633.4941835420001</v>
+        <v>630.8149175926001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1193032432323273</v>
+        <v>0.1216080901010973</v>
       </c>
       <c r="T72">
-        <v>1.697534485735041</v>
+        <v>1.750764205568068</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.620622816762107</v>
+        <v>3.569628129202077</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,22 +7228,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06793470992931822</v>
+        <v>0.06787020088893825</v>
       </c>
       <c r="C73">
-        <v>1414.59300355017</v>
+        <v>1361.98385447166</v>
       </c>
       <c r="D73">
-        <v>5155.92300355017</v>
+        <v>5161.54385447166</v>
       </c>
       <c r="E73">
-        <v>110.3299999999999</v>
+        <v>168.5599999999995</v>
       </c>
       <c r="F73">
-        <v>4134.33</v>
+        <v>4192.559999999999</v>
       </c>
       <c r="G73">
         <v>393</v>
@@ -7264,28 +7264,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M73">
-        <v>253.434429</v>
+        <v>257.003928</v>
       </c>
       <c r="N73">
-        <v>651.2322376666667</v>
+        <v>647.6627386666668</v>
       </c>
       <c r="O73">
-        <v>162.4173200740667</v>
+        <v>161.5270870234667</v>
       </c>
       <c r="P73">
-        <v>488.8149175926001</v>
+        <v>486.1356516432</v>
       </c>
       <c r="Q73">
-        <v>630.8149175926001</v>
+        <v>628.1356516432</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1216080901010973</v>
+        <v>0.1240775688890652</v>
       </c>
       <c r="T73">
-        <v>1.750764205568067</v>
+        <v>1.80779604824631</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.569628129202077</v>
+        <v>3.520049960740938</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,22 +7310,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06787020088893825</v>
+        <v>0.0693399182485583</v>
       </c>
       <c r="C74">
-        <v>1361.98385447166</v>
+        <v>1178.660719937719</v>
       </c>
       <c r="D74">
-        <v>5161.54385447166</v>
+        <v>5036.450719937719</v>
       </c>
       <c r="E74">
-        <v>168.5599999999995</v>
+        <v>226.79</v>
       </c>
       <c r="F74">
-        <v>4192.559999999999</v>
+        <v>4250.79</v>
       </c>
       <c r="G74">
         <v>393</v>
@@ -7346,45 +7346,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M74">
-        <v>257.003928</v>
+        <v>272.475639</v>
       </c>
       <c r="N74">
-        <v>647.6627386666668</v>
+        <v>632.1910276666667</v>
       </c>
       <c r="O74">
-        <v>161.5270870234667</v>
+        <v>157.6684423000667</v>
       </c>
       <c r="P74">
-        <v>486.1356516432</v>
+        <v>474.5225853666001</v>
       </c>
       <c r="Q74">
-        <v>628.1356516432</v>
+        <v>616.5225853666001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1240775688890652</v>
+        <v>0.1267299720316974</v>
       </c>
       <c r="T74">
-        <v>1.80779604824631</v>
+        <v>1.869052471863681</v>
       </c>
       <c r="U74">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V74">
         <v>0.2494</v>
       </c>
       <c r="W74">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.520049960740938</v>
+        <v>3.320174493348621</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,22 +7392,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0693399182485583</v>
+        <v>0.06929642600817834</v>
       </c>
       <c r="C75">
-        <v>1178.660719937719</v>
+        <v>1124.045384320281</v>
       </c>
       <c r="D75">
-        <v>5036.450719937719</v>
+        <v>5040.065384320281</v>
       </c>
       <c r="E75">
-        <v>226.79</v>
+        <v>285.0199999999995</v>
       </c>
       <c r="F75">
-        <v>4250.79</v>
+        <v>4309.02</v>
       </c>
       <c r="G75">
         <v>393</v>
@@ -7428,28 +7428,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M75">
-        <v>272.475639</v>
+        <v>276.208182</v>
       </c>
       <c r="N75">
-        <v>632.1910276666667</v>
+        <v>628.4584846666668</v>
       </c>
       <c r="O75">
-        <v>157.6684423000667</v>
+        <v>156.7375460758667</v>
       </c>
       <c r="P75">
-        <v>474.5225853666001</v>
+        <v>471.7209385908001</v>
       </c>
       <c r="Q75">
-        <v>616.5225853666001</v>
+        <v>613.7209385908001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1267299720316974</v>
+        <v>0.1295864061853013</v>
       </c>
       <c r="T75">
-        <v>1.869052471863681</v>
+        <v>1.935020928067004</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.320174493348621</v>
+        <v>3.275307270465532</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,22 +7474,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06929642600817834</v>
+        <v>0.06925293376779837</v>
       </c>
       <c r="C76">
-        <v>1124.045384320281</v>
+        <v>1069.435240923871</v>
       </c>
       <c r="D76">
-        <v>5040.065384320281</v>
+        <v>5043.685240923871</v>
       </c>
       <c r="E76">
-        <v>285.0199999999995</v>
+        <v>343.25</v>
       </c>
       <c r="F76">
-        <v>4309.02</v>
+        <v>4367.25</v>
       </c>
       <c r="G76">
         <v>393</v>
@@ -7510,28 +7510,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M76">
-        <v>276.208182</v>
+        <v>279.940725</v>
       </c>
       <c r="N76">
-        <v>628.4584846666668</v>
+        <v>624.7259416666667</v>
       </c>
       <c r="O76">
-        <v>156.7375460758667</v>
+        <v>155.8066498516667</v>
       </c>
       <c r="P76">
-        <v>471.7209385908001</v>
+        <v>468.919291815</v>
       </c>
       <c r="Q76">
-        <v>613.7209385908001</v>
+        <v>610.919291815</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1295864061853013</v>
+        <v>0.1326713550711935</v>
       </c>
       <c r="T76">
-        <v>1.935020928067004</v>
+        <v>2.006266860766594</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.275307270465532</v>
+        <v>3.231636506859324</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,22 +7556,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06925293376779837</v>
+        <v>0.06920944152741842</v>
       </c>
       <c r="C77">
-        <v>1069.435240923871</v>
+        <v>1014.830300943938</v>
       </c>
       <c r="D77">
-        <v>5043.685240923871</v>
+        <v>5047.310300943938</v>
       </c>
       <c r="E77">
-        <v>343.25</v>
+        <v>401.4800000000005</v>
       </c>
       <c r="F77">
-        <v>4367.25</v>
+        <v>4425.48</v>
       </c>
       <c r="G77">
         <v>393</v>
@@ -7592,28 +7592,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M77">
-        <v>279.940725</v>
+        <v>283.6732680000001</v>
       </c>
       <c r="N77">
-        <v>624.7259416666667</v>
+        <v>620.9933986666667</v>
       </c>
       <c r="O77">
-        <v>155.8066498516667</v>
+        <v>154.8757536274667</v>
       </c>
       <c r="P77">
-        <v>468.919291815</v>
+        <v>466.1176450392001</v>
       </c>
       <c r="Q77">
-        <v>610.919291815</v>
+        <v>608.1176450392001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1326713550711935</v>
+        <v>0.1360133830309101</v>
       </c>
       <c r="T77">
-        <v>2.006266860766594</v>
+        <v>2.083449954524482</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.231636506859324</v>
+        <v>3.189114973874333</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,22 +7638,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06920944152741842</v>
+        <v>0.06916594928703845</v>
       </c>
       <c r="C78">
-        <v>1014.830300943938</v>
+        <v>960.2305756081514</v>
       </c>
       <c r="D78">
-        <v>5047.310300943938</v>
+        <v>5050.940575608151</v>
       </c>
       <c r="E78">
-        <v>401.4800000000005</v>
+        <v>459.71</v>
       </c>
       <c r="F78">
-        <v>4425.48</v>
+        <v>4483.71</v>
       </c>
       <c r="G78">
         <v>393</v>
@@ -7674,28 +7674,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M78">
-        <v>283.6732680000001</v>
+        <v>287.405811</v>
       </c>
       <c r="N78">
-        <v>620.9933986666667</v>
+        <v>617.2608556666667</v>
       </c>
       <c r="O78">
-        <v>154.8757536274667</v>
+        <v>153.9448574032667</v>
       </c>
       <c r="P78">
-        <v>466.1176450392001</v>
+        <v>463.3159982634</v>
       </c>
       <c r="Q78">
-        <v>608.1176450392001</v>
+        <v>605.3159982633999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1360133830309101</v>
+        <v>0.1396460221175585</v>
       </c>
       <c r="T78">
-        <v>2.083449954524482</v>
+        <v>2.167344621652621</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.189114973874333</v>
+        <v>3.147697896291549</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,22 +7720,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06916594928703845</v>
+        <v>0.06912245704665848</v>
       </c>
       <c r="C79">
-        <v>960.2305756081514</v>
+        <v>905.6360761764918</v>
       </c>
       <c r="D79">
-        <v>5050.940575608151</v>
+        <v>5054.576076176492</v>
       </c>
       <c r="E79">
-        <v>459.71</v>
+        <v>517.9400000000005</v>
       </c>
       <c r="F79">
-        <v>4483.71</v>
+        <v>4541.940000000001</v>
       </c>
       <c r="G79">
         <v>393</v>
@@ -7756,28 +7756,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M79">
-        <v>287.405811</v>
+        <v>291.138354</v>
       </c>
       <c r="N79">
-        <v>617.2608556666667</v>
+        <v>613.5283126666667</v>
       </c>
       <c r="O79">
-        <v>153.9448574032667</v>
+        <v>153.0139611790667</v>
       </c>
       <c r="P79">
-        <v>463.3159982634</v>
+        <v>460.5143514876</v>
       </c>
       <c r="Q79">
-        <v>605.3159982633999</v>
+        <v>602.5143514876</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1396460221175585</v>
+        <v>0.143608901121175</v>
       </c>
       <c r="T79">
-        <v>2.167344621652621</v>
+        <v>2.258866076701501</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.147697896291549</v>
+        <v>3.107342795057042</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,22 +7802,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06912245704665848</v>
+        <v>0.06907896480627854</v>
       </c>
       <c r="C80">
-        <v>905.6360761764918</v>
+        <v>851.0468139413888</v>
       </c>
       <c r="D80">
-        <v>5054.576076176492</v>
+        <v>5058.216813941389</v>
       </c>
       <c r="E80">
-        <v>517.9400000000005</v>
+        <v>576.1700000000001</v>
       </c>
       <c r="F80">
-        <v>4541.940000000001</v>
+        <v>4600.17</v>
       </c>
       <c r="G80">
         <v>393</v>
@@ -7838,28 +7838,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M80">
-        <v>291.138354</v>
+        <v>294.870897</v>
       </c>
       <c r="N80">
-        <v>613.5283126666667</v>
+        <v>609.7957696666667</v>
       </c>
       <c r="O80">
-        <v>153.0139611790667</v>
+        <v>152.0830649548667</v>
       </c>
       <c r="P80">
-        <v>460.5143514876</v>
+        <v>457.7127047118</v>
       </c>
       <c r="Q80">
-        <v>602.5143514876</v>
+        <v>599.7127047118</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.143608901121175</v>
+        <v>0.147949197172755</v>
       </c>
       <c r="T80">
-        <v>2.258866076701501</v>
+        <v>2.359103860802655</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.107342795057042</v>
+        <v>3.068009341955054</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,22 +7884,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06907896480627854</v>
+        <v>0.06903547256589856</v>
       </c>
       <c r="C81">
-        <v>851.0468139413888</v>
+        <v>796.4628002278323</v>
       </c>
       <c r="D81">
-        <v>5058.216813941389</v>
+        <v>5061.862800227833</v>
       </c>
       <c r="E81">
-        <v>576.1700000000001</v>
+        <v>634.4000000000005</v>
       </c>
       <c r="F81">
-        <v>4600.17</v>
+        <v>4658.400000000001</v>
       </c>
       <c r="G81">
         <v>393</v>
@@ -7920,28 +7920,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M81">
-        <v>294.870897</v>
+        <v>298.60344</v>
       </c>
       <c r="N81">
-        <v>609.7957696666667</v>
+        <v>606.0632266666667</v>
       </c>
       <c r="O81">
-        <v>152.0830649548667</v>
+        <v>151.1521687306667</v>
       </c>
       <c r="P81">
-        <v>457.7127047118</v>
+        <v>454.911057936</v>
       </c>
       <c r="Q81">
-        <v>599.7127047118</v>
+        <v>596.911057936</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.147949197172755</v>
+        <v>0.1527235228294929</v>
       </c>
       <c r="T81">
-        <v>2.359103860802655</v>
+        <v>2.469365423313924</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.068009341955054</v>
+        <v>3.029659225180616</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,22 +7966,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06903547256589856</v>
+        <v>0.07373427112551861</v>
       </c>
       <c r="C82">
-        <v>796.4628002278323</v>
+        <v>372.5243466383681</v>
       </c>
       <c r="D82">
-        <v>5061.862800227833</v>
+        <v>4696.154346638368</v>
       </c>
       <c r="E82">
-        <v>634.4000000000005</v>
+        <v>692.6300000000001</v>
       </c>
       <c r="F82">
-        <v>4658.400000000001</v>
+        <v>4716.63</v>
       </c>
       <c r="G82">
         <v>393</v>
@@ -8002,45 +8002,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M82">
-        <v>298.60344</v>
+        <v>339.1256970000001</v>
       </c>
       <c r="N82">
-        <v>606.0632266666667</v>
+        <v>565.5409696666667</v>
       </c>
       <c r="O82">
-        <v>151.1521687306667</v>
+        <v>141.0459178348667</v>
       </c>
       <c r="P82">
-        <v>454.911057936</v>
+        <v>424.4950518318</v>
       </c>
       <c r="Q82">
-        <v>596.911057936</v>
+        <v>566.4950518318</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1527235228294929</v>
+        <v>0.1580004090816769</v>
       </c>
       <c r="T82">
-        <v>2.469365423313924</v>
+        <v>2.591233466089537</v>
       </c>
       <c r="U82">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V82">
         <v>0.2494</v>
       </c>
       <c r="W82">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.029659225180616</v>
+        <v>2.66764410562101</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,22 +8048,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07373427112551861</v>
+        <v>0.07374932568513864</v>
       </c>
       <c r="C83">
-        <v>372.5243466383681</v>
+        <v>313.2075514574262</v>
       </c>
       <c r="D83">
-        <v>4696.154346638368</v>
+        <v>4695.067551457427</v>
       </c>
       <c r="E83">
-        <v>692.6300000000001</v>
+        <v>750.8600000000006</v>
       </c>
       <c r="F83">
-        <v>4716.63</v>
+        <v>4774.860000000001</v>
       </c>
       <c r="G83">
         <v>393</v>
@@ -8084,28 +8084,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M83">
-        <v>339.1256970000001</v>
+        <v>343.3124340000001</v>
       </c>
       <c r="N83">
-        <v>565.5409696666667</v>
+        <v>561.3542326666667</v>
       </c>
       <c r="O83">
-        <v>141.0459178348667</v>
+        <v>140.0017456270667</v>
       </c>
       <c r="P83">
-        <v>424.4950518318</v>
+        <v>421.3524870396</v>
       </c>
       <c r="Q83">
-        <v>566.4950518318</v>
+        <v>563.3524870396</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1580004090816769</v>
+        <v>0.1638636160285481</v>
       </c>
       <c r="T83">
-        <v>2.591233466089537</v>
+        <v>2.726642402506885</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.66764410562101</v>
+        <v>2.63511186043051</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,22 +8130,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07374932568513864</v>
+        <v>0.07376438024475868</v>
       </c>
       <c r="C84">
-        <v>313.2075514574262</v>
+        <v>253.8912591775415</v>
       </c>
       <c r="D84">
-        <v>4695.067551457427</v>
+        <v>4693.981259177542</v>
       </c>
       <c r="E84">
-        <v>750.8600000000006</v>
+        <v>809.0900000000001</v>
       </c>
       <c r="F84">
-        <v>4774.860000000001</v>
+        <v>4833.09</v>
       </c>
       <c r="G84">
         <v>393</v>
@@ -8166,28 +8166,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M84">
-        <v>343.3124340000001</v>
+        <v>347.499171</v>
       </c>
       <c r="N84">
-        <v>561.3542326666667</v>
+        <v>557.1674956666667</v>
       </c>
       <c r="O84">
-        <v>140.0017456270667</v>
+        <v>138.9575734192667</v>
       </c>
       <c r="P84">
-        <v>421.3524870396</v>
+        <v>418.2099222474</v>
       </c>
       <c r="Q84">
-        <v>563.3524870396</v>
+        <v>560.2099222474001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1638636160285481</v>
+        <v>0.1704166120279923</v>
       </c>
       <c r="T84">
-        <v>2.726642402506885</v>
+        <v>2.877981802032155</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8204,7 +8204,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.63511186043051</v>
+        <v>2.603363524762672</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,22 +8212,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07376438024475868</v>
+        <v>0.07377943480437872</v>
       </c>
       <c r="C85">
-        <v>253.8912591775415</v>
+        <v>194.5754694497246</v>
       </c>
       <c r="D85">
-        <v>4693.981259177542</v>
+        <v>4692.895469449725</v>
       </c>
       <c r="E85">
-        <v>809.0900000000001</v>
+        <v>867.3200000000006</v>
       </c>
       <c r="F85">
-        <v>4833.09</v>
+        <v>4891.320000000001</v>
       </c>
       <c r="G85">
         <v>393</v>
@@ -8248,28 +8248,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M85">
-        <v>347.499171</v>
+        <v>351.6859080000001</v>
       </c>
       <c r="N85">
-        <v>557.1674956666667</v>
+        <v>552.9807586666666</v>
       </c>
       <c r="O85">
-        <v>138.9575734192667</v>
+        <v>137.9134012114667</v>
       </c>
       <c r="P85">
-        <v>418.2099222474</v>
+        <v>415.0673574552</v>
       </c>
       <c r="Q85">
-        <v>560.2099222474001</v>
+        <v>557.0673574552</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1704166120279923</v>
+        <v>0.1777887325273671</v>
       </c>
       <c r="T85">
-        <v>2.877981802032155</v>
+        <v>3.048238626498086</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8286,7 +8286,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.603363524762672</v>
+        <v>2.57237110184883</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,22 +8294,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07377943480437874</v>
+        <v>0.07379448936399877</v>
       </c>
       <c r="C86">
-        <v>194.5754694497236</v>
+        <v>135.260181925315</v>
       </c>
       <c r="D86">
-        <v>4692.895469449723</v>
+        <v>4691.810181925315</v>
       </c>
       <c r="E86">
-        <v>867.3199999999997</v>
+        <v>925.5500000000002</v>
       </c>
       <c r="F86">
-        <v>4891.32</v>
+        <v>4949.55</v>
       </c>
       <c r="G86">
         <v>393</v>
@@ -8330,28 +8330,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M86">
-        <v>351.685908</v>
+        <v>355.872645</v>
       </c>
       <c r="N86">
-        <v>552.9807586666668</v>
+        <v>548.7940216666667</v>
       </c>
       <c r="O86">
-        <v>137.9134012114667</v>
+        <v>136.8692290036667</v>
       </c>
       <c r="P86">
-        <v>415.0673574552001</v>
+        <v>411.9247926630001</v>
       </c>
       <c r="Q86">
-        <v>557.0673574552001</v>
+        <v>553.9247926630001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.177788732527367</v>
+        <v>0.1861438024266585</v>
       </c>
       <c r="T86">
-        <v>3.048238626498084</v>
+        <v>3.241196360892805</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.572371101848832</v>
+        <v>2.542107912415315</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,22 +8376,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07379448936399877</v>
+        <v>0.0738095439236188</v>
       </c>
       <c r="C87">
-        <v>135.260181925315</v>
+        <v>75.94539625597099</v>
       </c>
       <c r="D87">
-        <v>4691.810181925315</v>
+        <v>4690.725396255971</v>
       </c>
       <c r="E87">
-        <v>925.5500000000002</v>
+        <v>983.7799999999997</v>
       </c>
       <c r="F87">
-        <v>4949.55</v>
+        <v>5007.78</v>
       </c>
       <c r="G87">
         <v>393</v>
@@ -8412,28 +8412,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M87">
-        <v>355.872645</v>
+        <v>360.059382</v>
       </c>
       <c r="N87">
-        <v>548.7940216666667</v>
+        <v>544.6072846666667</v>
       </c>
       <c r="O87">
-        <v>136.8692290036667</v>
+        <v>135.8250567958667</v>
       </c>
       <c r="P87">
-        <v>411.9247926630001</v>
+        <v>408.7822278708001</v>
       </c>
       <c r="Q87">
-        <v>553.9247926630001</v>
+        <v>550.7822278708001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1861438024266585</v>
+        <v>0.1956924537401343</v>
       </c>
       <c r="T87">
-        <v>3.241196360892805</v>
+        <v>3.461719485915343</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8450,7 +8450,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.542107912415315</v>
+        <v>2.512548518084905</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,22 +8458,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0738095439236188</v>
+        <v>0.07637138428323884</v>
       </c>
       <c r="C88">
-        <v>75.94539625597099</v>
+        <v>-159.8538979553859</v>
       </c>
       <c r="D88">
-        <v>4690.725396255971</v>
+        <v>4513.156102044614</v>
       </c>
       <c r="E88">
-        <v>983.7799999999997</v>
+        <v>1042.01</v>
       </c>
       <c r="F88">
-        <v>5007.78</v>
+        <v>5066.01</v>
       </c>
       <c r="G88">
         <v>393</v>
@@ -8494,45 +8494,45 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M88">
-        <v>360.059382</v>
+        <v>384.0035580000001</v>
       </c>
       <c r="N88">
-        <v>544.6072846666667</v>
+        <v>520.6631086666666</v>
       </c>
       <c r="O88">
-        <v>135.8250567958667</v>
+        <v>129.8533793014667</v>
       </c>
       <c r="P88">
-        <v>408.7822278708001</v>
+        <v>390.8097293651999</v>
       </c>
       <c r="Q88">
-        <v>550.7822278708001</v>
+        <v>532.8097293651999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1956924537401343</v>
+        <v>0.2067101283326065</v>
       </c>
       <c r="T88">
-        <v>3.461719485915343</v>
+        <v>3.716169245556732</v>
       </c>
       <c r="U88">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V88">
         <v>0.2494</v>
       </c>
       <c r="W88">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.512548518084905</v>
+        <v>2.355880949068359</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,22 +8540,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07637138428323884</v>
+        <v>0.0764157122428589</v>
       </c>
       <c r="C89">
-        <v>-159.8538979553859</v>
+        <v>-221.0381634017403</v>
       </c>
       <c r="D89">
-        <v>4513.156102044614</v>
+        <v>4510.201836598259</v>
       </c>
       <c r="E89">
-        <v>1042.01</v>
+        <v>1100.24</v>
       </c>
       <c r="F89">
-        <v>5066.01</v>
+        <v>5124.24</v>
       </c>
       <c r="G89">
         <v>393</v>
@@ -8576,28 +8576,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M89">
-        <v>384.0035580000001</v>
+        <v>388.417392</v>
       </c>
       <c r="N89">
-        <v>520.6631086666666</v>
+        <v>516.2492746666667</v>
       </c>
       <c r="O89">
-        <v>129.8533793014667</v>
+        <v>128.7525691018667</v>
       </c>
       <c r="P89">
-        <v>390.8097293651999</v>
+        <v>387.4967055648</v>
       </c>
       <c r="Q89">
-        <v>532.8097293651999</v>
+        <v>529.4967055648</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2067101283326065</v>
+        <v>0.2195640820238241</v>
       </c>
       <c r="T89">
-        <v>3.716169245556732</v>
+        <v>4.013027298471687</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.355880949068359</v>
+        <v>2.329109574647128</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,22 +8622,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0764157122428589</v>
+        <v>0.07646004020247893</v>
       </c>
       <c r="C90">
-        <v>-221.0381634017403</v>
+        <v>-282.2185637147741</v>
       </c>
       <c r="D90">
-        <v>4510.201836598259</v>
+        <v>4507.251436285226</v>
       </c>
       <c r="E90">
-        <v>1100.24</v>
+        <v>1158.47</v>
       </c>
       <c r="F90">
-        <v>5124.24</v>
+        <v>5182.47</v>
       </c>
       <c r="G90">
         <v>393</v>
@@ -8658,28 +8658,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M90">
-        <v>388.417392</v>
+        <v>392.8312260000001</v>
       </c>
       <c r="N90">
-        <v>516.2492746666667</v>
+        <v>511.8354406666667</v>
       </c>
       <c r="O90">
-        <v>128.7525691018667</v>
+        <v>127.6517589022667</v>
       </c>
       <c r="P90">
-        <v>387.4967055648</v>
+        <v>384.1836817644</v>
       </c>
       <c r="Q90">
-        <v>529.4967055648</v>
+        <v>526.1836817644</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2195640820238241</v>
+        <v>0.2347551182043539</v>
       </c>
       <c r="T90">
-        <v>4.013027298471687</v>
+        <v>4.363859542825725</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8696,7 +8696,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.329109574647128</v>
+        <v>2.302939804145474</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,22 +8704,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07646004020247893</v>
+        <v>0.07650436816209896</v>
       </c>
       <c r="C91">
-        <v>-282.2185637147741</v>
+        <v>-343.3951064747935</v>
       </c>
       <c r="D91">
-        <v>4507.251436285226</v>
+        <v>4504.304893525206</v>
       </c>
       <c r="E91">
-        <v>1158.47</v>
+        <v>1216.7</v>
       </c>
       <c r="F91">
-        <v>5182.47</v>
+        <v>5240.7</v>
       </c>
       <c r="G91">
         <v>393</v>
@@ -8740,28 +8740,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M91">
-        <v>392.8312260000001</v>
+        <v>397.24506</v>
       </c>
       <c r="N91">
-        <v>511.8354406666667</v>
+        <v>507.4216066666667</v>
       </c>
       <c r="O91">
-        <v>127.6517589022667</v>
+        <v>126.5509487026667</v>
       </c>
       <c r="P91">
-        <v>384.1836817644</v>
+        <v>380.870657964</v>
       </c>
       <c r="Q91">
-        <v>526.1836817644</v>
+        <v>522.870657964</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2347551182043539</v>
+        <v>0.2529843616209897</v>
       </c>
       <c r="T91">
-        <v>4.363859542825725</v>
+        <v>4.78485823605057</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.302939804145474</v>
+        <v>2.277351584099414</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,22 +8786,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07650436816209896</v>
+        <v>0.076548696121719</v>
       </c>
       <c r="C92">
-        <v>-343.3951064747935</v>
+        <v>-404.5677992422952</v>
       </c>
       <c r="D92">
-        <v>4504.304893525206</v>
+        <v>4501.362200757705</v>
       </c>
       <c r="E92">
-        <v>1216.7</v>
+        <v>1274.93</v>
       </c>
       <c r="F92">
-        <v>5240.7</v>
+        <v>5298.93</v>
       </c>
       <c r="G92">
         <v>393</v>
@@ -8822,28 +8822,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M92">
-        <v>397.24506</v>
+        <v>401.658894</v>
       </c>
       <c r="N92">
-        <v>507.4216066666667</v>
+        <v>503.0077726666667</v>
       </c>
       <c r="O92">
-        <v>126.5509487026667</v>
+        <v>125.4501385030667</v>
       </c>
       <c r="P92">
-        <v>380.870657964</v>
+        <v>377.5576341636</v>
       </c>
       <c r="Q92">
-        <v>522.870657964</v>
+        <v>519.5576341636</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2529843616209897</v>
+        <v>0.2752645480191001</v>
       </c>
       <c r="T92">
-        <v>4.78485823605057</v>
+        <v>5.299412194436492</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.277351584099414</v>
+        <v>2.252325742515904</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,22 +8868,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.076548696121719</v>
+        <v>0.07659302408133906</v>
       </c>
       <c r="C93">
-        <v>-404.5677992422952</v>
+        <v>-465.7366495580327</v>
       </c>
       <c r="D93">
-        <v>4501.362200757705</v>
+        <v>4498.423350441967</v>
       </c>
       <c r="E93">
-        <v>1274.93</v>
+        <v>1333.16</v>
       </c>
       <c r="F93">
-        <v>5298.93</v>
+        <v>5357.16</v>
       </c>
       <c r="G93">
         <v>393</v>
@@ -8904,28 +8904,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M93">
-        <v>401.658894</v>
+        <v>406.072728</v>
       </c>
       <c r="N93">
-        <v>503.0077726666667</v>
+        <v>498.5939386666667</v>
       </c>
       <c r="O93">
-        <v>125.4501385030667</v>
+        <v>124.3493283034667</v>
       </c>
       <c r="P93">
-        <v>377.5576341636</v>
+        <v>374.2446103632</v>
       </c>
       <c r="Q93">
-        <v>519.5576341636</v>
+        <v>516.2446103632001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2752645480191001</v>
+        <v>0.3031147810167382</v>
       </c>
       <c r="T93">
-        <v>5.299412194436492</v>
+        <v>5.942604642418896</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.252325742515904</v>
+        <v>2.227843940966818</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,22 +8950,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07659302408133906</v>
+        <v>0.07663735204095909</v>
       </c>
       <c r="C94">
-        <v>-465.7366495580327</v>
+        <v>-526.9016649430741</v>
       </c>
       <c r="D94">
-        <v>4498.423350441967</v>
+        <v>4495.488335056926</v>
       </c>
       <c r="E94">
-        <v>1333.16</v>
+        <v>1391.39</v>
       </c>
       <c r="F94">
-        <v>5357.16</v>
+        <v>5415.39</v>
       </c>
       <c r="G94">
         <v>393</v>
@@ -8986,28 +8986,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M94">
-        <v>406.072728</v>
+        <v>410.486562</v>
       </c>
       <c r="N94">
-        <v>498.5939386666667</v>
+        <v>494.1801046666667</v>
       </c>
       <c r="O94">
-        <v>124.3493283034667</v>
+        <v>123.2485181038667</v>
       </c>
       <c r="P94">
-        <v>374.2446103632</v>
+        <v>370.9315865628</v>
       </c>
       <c r="Q94">
-        <v>516.2446103632001</v>
+        <v>512.9315865628</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3031147810167382</v>
+        <v>0.3389222234422728</v>
       </c>
       <c r="T94">
-        <v>5.942604642418896</v>
+        <v>6.769566361253413</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.227843940966818</v>
+        <v>2.203888629773626</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,22 +9032,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07663735204095909</v>
+        <v>0.07668168000057912</v>
       </c>
       <c r="C95">
-        <v>-526.9016649430741</v>
+        <v>-588.0628528988764</v>
       </c>
       <c r="D95">
-        <v>4495.488335056926</v>
+        <v>4492.557147101124</v>
       </c>
       <c r="E95">
-        <v>1391.39</v>
+        <v>1449.62</v>
       </c>
       <c r="F95">
-        <v>5415.39</v>
+        <v>5473.62</v>
       </c>
       <c r="G95">
         <v>393</v>
@@ -9068,28 +9068,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M95">
-        <v>410.486562</v>
+        <v>414.900396</v>
       </c>
       <c r="N95">
-        <v>494.1801046666667</v>
+        <v>489.7662706666667</v>
       </c>
       <c r="O95">
-        <v>123.2485181038667</v>
+        <v>122.1477079042667</v>
       </c>
       <c r="P95">
-        <v>370.9315865628</v>
+        <v>367.6185627624001</v>
       </c>
       <c r="Q95">
-        <v>512.9315865628</v>
+        <v>509.6185627624001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3389222234422728</v>
+        <v>0.3866654800096523</v>
       </c>
       <c r="T95">
-        <v>6.769566361253413</v>
+        <v>7.872181986366105</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.203888629773626</v>
+        <v>2.18044300605263</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,22 +9114,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07668168000057912</v>
+        <v>0.07672600796019916</v>
       </c>
       <c r="C96">
-        <v>-588.0628528988764</v>
+        <v>-649.2202209073466</v>
       </c>
       <c r="D96">
-        <v>4492.557147101124</v>
+        <v>4489.629779092654</v>
       </c>
       <c r="E96">
-        <v>1449.62</v>
+        <v>1507.85</v>
       </c>
       <c r="F96">
-        <v>5473.62</v>
+        <v>5531.85</v>
       </c>
       <c r="G96">
         <v>393</v>
@@ -9150,28 +9150,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M96">
-        <v>414.900396</v>
+        <v>419.3142300000001</v>
       </c>
       <c r="N96">
-        <v>489.7662706666667</v>
+        <v>485.3524366666667</v>
       </c>
       <c r="O96">
-        <v>122.1477079042667</v>
+        <v>121.0468977046667</v>
       </c>
       <c r="P96">
-        <v>367.6185627624001</v>
+        <v>364.305538962</v>
       </c>
       <c r="Q96">
-        <v>509.6185627624001</v>
+        <v>506.305538962</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3866654800096523</v>
+        <v>0.4535060392039838</v>
       </c>
       <c r="T96">
-        <v>7.872181986366105</v>
+        <v>9.415843861523875</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.18044300605263</v>
+        <v>2.157490974409971</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,22 +9196,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07672600796019916</v>
+        <v>0.0767703359198192</v>
       </c>
       <c r="C97">
-        <v>-649.2202209073466</v>
+        <v>-710.3737764308989</v>
       </c>
       <c r="D97">
-        <v>4489.629779092654</v>
+        <v>4486.706223569102</v>
       </c>
       <c r="E97">
-        <v>1507.85</v>
+        <v>1566.080000000001</v>
       </c>
       <c r="F97">
-        <v>5531.85</v>
+        <v>5590.080000000001</v>
       </c>
       <c r="G97">
         <v>393</v>
@@ -9232,28 +9232,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M97">
-        <v>419.3142300000001</v>
+        <v>423.7280640000001</v>
       </c>
       <c r="N97">
-        <v>485.3524366666667</v>
+        <v>480.9386026666667</v>
       </c>
       <c r="O97">
-        <v>121.0468977046667</v>
+        <v>119.9460875050667</v>
       </c>
       <c r="P97">
-        <v>364.305538962</v>
+        <v>360.9925151616</v>
       </c>
       <c r="Q97">
-        <v>506.305538962</v>
+        <v>502.9925151616</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4535060392039838</v>
+        <v>0.553766877995481</v>
       </c>
       <c r="T97">
-        <v>9.415843861523875</v>
+        <v>11.73133667426053</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9270,7 +9270,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.157490974409971</v>
+        <v>2.1350171100932</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,22 +9278,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07677033591981919</v>
+        <v>0.07681466387943924</v>
       </c>
       <c r="C98">
-        <v>-710.3737764308971</v>
+        <v>-771.5235269125214</v>
       </c>
       <c r="D98">
-        <v>4486.706223569103</v>
+        <v>4483.786473087478</v>
       </c>
       <c r="E98">
-        <v>1566.08</v>
+        <v>1624.309999999999</v>
       </c>
       <c r="F98">
-        <v>5590.08</v>
+        <v>5648.309999999999</v>
       </c>
       <c r="G98">
         <v>393</v>
@@ -9314,28 +9314,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M98">
-        <v>423.728064</v>
+        <v>428.141898</v>
       </c>
       <c r="N98">
-        <v>480.9386026666667</v>
+        <v>476.5247686666668</v>
       </c>
       <c r="O98">
-        <v>119.9460875050667</v>
+        <v>118.8452773054667</v>
       </c>
       <c r="P98">
-        <v>360.9925151616001</v>
+        <v>357.6794913612001</v>
       </c>
       <c r="Q98">
-        <v>502.9925151616001</v>
+        <v>499.6794913612001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5537668779954794</v>
+        <v>0.7208682759813074</v>
       </c>
       <c r="T98">
-        <v>11.7313366742605</v>
+        <v>15.59049136215491</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9352,7 +9352,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.135017110093201</v>
+        <v>2.113006624422137</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,22 +9360,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07681466387943924</v>
+        <v>0.07685899183905928</v>
       </c>
       <c r="C99">
-        <v>-771.5235269125214</v>
+        <v>-832.6694797758482</v>
       </c>
       <c r="D99">
-        <v>4483.786473087478</v>
+        <v>4480.870520224152</v>
       </c>
       <c r="E99">
-        <v>1624.309999999999</v>
+        <v>1682.54</v>
       </c>
       <c r="F99">
-        <v>5648.309999999999</v>
+        <v>5706.54</v>
       </c>
       <c r="G99">
         <v>393</v>
@@ -9396,28 +9396,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M99">
-        <v>428.141898</v>
+        <v>432.555732</v>
       </c>
       <c r="N99">
-        <v>476.5247686666668</v>
+        <v>472.1109346666667</v>
       </c>
       <c r="O99">
-        <v>118.8452773054667</v>
+        <v>117.7444671058667</v>
       </c>
       <c r="P99">
-        <v>357.6794913612001</v>
+        <v>354.3664675608001</v>
       </c>
       <c r="Q99">
-        <v>499.6794913612001</v>
+        <v>496.3664675608001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7208682759813074</v>
+        <v>1.055071071952963</v>
       </c>
       <c r="T99">
-        <v>15.59049136215491</v>
+        <v>23.30880073794372</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.113006624422137</v>
+        <v>2.091445332336196</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,22 +9442,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07685899183905928</v>
+        <v>0.07690331979867931</v>
       </c>
       <c r="C100">
-        <v>-832.6694797758482</v>
+        <v>-893.8116424252066</v>
       </c>
       <c r="D100">
-        <v>4480.870520224152</v>
+        <v>4477.958357574793</v>
       </c>
       <c r="E100">
-        <v>1682.54</v>
+        <v>1740.77</v>
       </c>
       <c r="F100">
-        <v>5706.54</v>
+        <v>5764.77</v>
       </c>
       <c r="G100">
         <v>393</v>
@@ -9478,28 +9478,28 @@
         <v>904.6666666666667</v>
       </c>
       <c r="M100">
-        <v>432.555732</v>
+        <v>436.969566</v>
       </c>
       <c r="N100">
-        <v>472.1109346666667</v>
+        <v>467.6971006666668</v>
       </c>
       <c r="O100">
-        <v>117.7444671058667</v>
+        <v>116.6436569062667</v>
       </c>
       <c r="P100">
-        <v>354.3664675608001</v>
+        <v>351.0534437604001</v>
       </c>
       <c r="Q100">
-        <v>496.3664675608001</v>
+        <v>493.0534437604001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.055071071952963</v>
+        <v>2.05767945986793</v>
       </c>
       <c r="T100">
-        <v>23.30880073794372</v>
+        <v>46.46372886531016</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9516,91 +9516,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.091445332336196</v>
+        <v>2.070319621908558</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07690331979867931</v>
-      </c>
-      <c r="C101">
-        <v>-893.8116424252066</v>
-      </c>
-      <c r="D101">
-        <v>4477.958357574793</v>
-      </c>
-      <c r="E101">
-        <v>1740.77</v>
-      </c>
-      <c r="F101">
-        <v>5764.77</v>
-      </c>
-      <c r="G101">
-        <v>393</v>
-      </c>
-      <c r="H101">
-        <v>1799</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1046.666666666667</v>
-      </c>
-      <c r="K101">
-        <v>142</v>
-      </c>
-      <c r="L101">
-        <v>904.6666666666667</v>
-      </c>
-      <c r="M101">
-        <v>436.969566</v>
-      </c>
-      <c r="N101">
-        <v>467.6971006666668</v>
-      </c>
-      <c r="O101">
-        <v>116.6436569062667</v>
-      </c>
-      <c r="P101">
-        <v>351.0534437604001</v>
-      </c>
-      <c r="Q101">
-        <v>493.0534437604001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.05767945986793</v>
-      </c>
-      <c r="T101">
-        <v>46.46372886531016</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2494</v>
-      </c>
-      <c r="W101">
-        <v>0.05689548</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.070319621908558</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
